--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>7.28</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>8.75</v>
+        <v>1.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.05</v>
+        <v>3.88</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>4.75</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>7.28</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.76</v>
+        <v>2.68</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.54</v>
+        <v>3.22</v>
       </c>
       <c r="R34" t="n">
-        <v>4.61</v>
+        <v>2.57</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="R36" t="n">
-        <v>2.61</v>
+        <v>2.96</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.22</v>
+        <v>3.54</v>
       </c>
       <c r="R37" t="n">
-        <v>2.57</v>
+        <v>4.9</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.68</v>
+        <v>1.31</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.18</v>
+        <v>5.05</v>
       </c>
       <c r="R38" t="n">
-        <v>2.6</v>
+        <v>9.4</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.31</v>
+        <v>1.79</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.05</v>
+        <v>3.65</v>
       </c>
       <c r="R39" t="n">
-        <v>9.4</v>
+        <v>4.27</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q43" t="n">
         <v>3.54</v>
       </c>
       <c r="R43" t="n">
-        <v>4.9</v>
+        <v>4.61</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8926,7 +8926,7 @@
         <v>1.98</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.99</v>
+        <v>2.47</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.65</v>
+        <v>3.18</v>
       </c>
       <c r="R132" t="n">
-        <v>3.44</v>
+        <v>2.84</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26459,7 +26459,7 @@
         <v>2.05</v>
       </c>
       <c r="AF132" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29017,16 +29017,16 @@
         <v>0</v>
       </c>
       <c r="AE145" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF145" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG145" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH145" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,16 +30199,16 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF151" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG151" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH151" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI151" t="n">
         <v>0</v>
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF153" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30987,10 +30987,10 @@
         <v>0</v>
       </c>
       <c r="AE155" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF155" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG155" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.26</v>
+        <v>1.66</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="R171" t="n">
-        <v>3.2</v>
+        <v>5.23</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34139,10 +34139,10 @@
         <v>0</v>
       </c>
       <c r="AE171" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF171" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG171" t="n">
         <v>0</v>
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="R183" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AF183" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="Q184" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="R184" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36700,10 +36700,10 @@
         <v>0</v>
       </c>
       <c r="AE184" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF184" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG184" t="n">
         <v>0</v>
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="R194" t="n">
-        <v>5.23</v>
+        <v>3</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AF194" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI197"/>
+  <dimension ref="A1:BI199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2127,27 +2127,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46115.33333333334</v>
+        <v>46115.29166666666</v>
       </c>
     </row>
     <row r="10">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46115.35416666666</v>
+        <v>46115.33333333334</v>
       </c>
     </row>
     <row r="12">
@@ -2718,27 +2718,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46115.35416666666</v>
+        <v>46115.33333333334</v>
       </c>
     </row>
     <row r="13">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>8.75</v>
+        <v>1.36</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.05</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>7.28</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>7.28</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3506,27 +3506,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46115.35763888889</v>
+        <v>46115.35416666666</v>
       </c>
     </row>
     <row r="17">
@@ -3703,27 +3703,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46115.375</v>
+        <v>46115.35416666666</v>
       </c>
     </row>
     <row r="18">
@@ -3900,27 +3900,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46115.375</v>
+        <v>46115.35763888889</v>
       </c>
     </row>
     <row r="19">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46115.41666666666</v>
+        <v>46115.375</v>
       </c>
     </row>
     <row r="20">
@@ -4294,27 +4294,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46115.41666666666</v>
+        <v>46115.375</v>
       </c>
     </row>
     <row r="21">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5082,27 +5082,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46115.4375</v>
+        <v>46115.41666666666</v>
       </c>
     </row>
     <row r="25">
@@ -5279,27 +5279,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46115.4375</v>
+        <v>46115.41666666666</v>
       </c>
     </row>
     <row r="26">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46115.45138888889</v>
+        <v>46115.4375</v>
       </c>
     </row>
     <row r="29">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46115.45833333334</v>
+        <v>46115.4375</v>
       </c>
     </row>
     <row r="30">
@@ -6264,27 +6264,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46115.45833333334</v>
+        <v>46115.45138888889</v>
       </c>
     </row>
     <row r="31">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.68</v>
+        <v>1.76</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.18</v>
+        <v>3.54</v>
       </c>
       <c r="R42" t="n">
-        <v>2.6</v>
+        <v>4.61</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.72</v>
+        <v>3.64</v>
       </c>
       <c r="R62" t="n">
-        <v>9.07</v>
+        <v>3.96</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,7 +12666,7 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF62" t="n">
         <v>1.9</v>
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46115.47916666666</v>
+        <v>46115.45833333334</v>
       </c>
     </row>
     <row r="63">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
-        <v>46115.47916666666</v>
+        <v>46115.45833333334</v>
       </c>
     </row>
     <row r="64">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>9.07</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13159,12 +13159,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46115.5</v>
+        <v>46115.47916666666</v>
       </c>
     </row>
     <row r="66">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46115.5</v>
+        <v>46115.47916666666</v>
       </c>
     </row>
     <row r="67">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13947,27 +13947,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>46115.51041666666</v>
+        <v>46115.5</v>
       </c>
     </row>
     <row r="70">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14332,7 +14332,7 @@
         <v>0</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>46115.52083333334</v>
+        <v>46115.5</v>
       </c>
     </row>
     <row r="71">
@@ -14341,27 +14341,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46115.52083333334</v>
+        <v>46115.51041666666</v>
       </c>
     </row>
     <row r="72">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>46115.54166666666</v>
+        <v>46115.52083333334</v>
       </c>
     </row>
     <row r="74">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>46115.54166666666</v>
+        <v>46115.52083333334</v>
       </c>
     </row>
     <row r="75">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16902,12 +16902,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17090,7 +17090,7 @@
         <v>0</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>46115.55208333334</v>
+        <v>46115.54166666666</v>
       </c>
     </row>
     <row r="85">
@@ -17099,12 +17099,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,142 +17152,142 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W85" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI85" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ85" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL85" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM85" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN85" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO85" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AR85" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AS85" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AT85" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AU85" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AV85" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AW85" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX85" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AY85" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AZ85" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BA85" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BB85" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC85" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD85" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE85" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF85" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG85" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BH85" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>46115.55208333334</v>
+        <v>46115.54166666666</v>
       </c>
     </row>
     <row r="86">
@@ -17296,12 +17296,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17484,7 +17484,7 @@
         <v>0</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>46115.5625</v>
+        <v>46115.54166666666</v>
       </c>
     </row>
     <row r="87">
@@ -17493,12 +17493,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17681,7 +17681,7 @@
         <v>0</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>46115.57291666666</v>
+        <v>46115.55208333334</v>
       </c>
     </row>
     <row r="88">
@@ -17690,12 +17690,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,142 +17743,142 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V88" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI88" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL88" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP88" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR88" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AS88" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AU88" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AV88" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW88" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AY88" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BA88" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BB88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC88" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD88" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE88" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF88" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG88" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BH88" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>46115.57291666666</v>
+        <v>46115.55208333334</v>
       </c>
     </row>
     <row r="89">
@@ -17887,12 +17887,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18075,7 +18075,7 @@
         <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>46115.57291666666</v>
+        <v>46115.5625</v>
       </c>
     </row>
     <row r="90">
@@ -18084,12 +18084,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18272,7 +18272,7 @@
         <v>0</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>46115.58333333334</v>
+        <v>46115.57291666666</v>
       </c>
     </row>
     <row r="91">
@@ -18281,12 +18281,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46115.58333333334</v>
+        <v>46115.57291666666</v>
       </c>
     </row>
     <row r="92">
@@ -18478,12 +18478,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>46115.58333333334</v>
+        <v>46115.57291666666</v>
       </c>
     </row>
     <row r="93">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46115.60416666666</v>
+        <v>46115.58333333334</v>
       </c>
     </row>
     <row r="102">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20636,7 +20636,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3" t="n">
-        <v>46115.60416666666</v>
+        <v>46115.58333333334</v>
       </c>
     </row>
     <row r="103">
@@ -20645,12 +20645,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20833,7 +20833,7 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3" t="n">
-        <v>46115.60416666666</v>
+        <v>46115.58333333334</v>
       </c>
     </row>
     <row r="104">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23009,12 +23009,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23197,7 +23197,7 @@
         <v>0</v>
       </c>
       <c r="BI115" s="3" t="n">
-        <v>46115.625</v>
+        <v>46115.60416666666</v>
       </c>
     </row>
     <row r="116">
@@ -23206,12 +23206,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23394,7 +23394,7 @@
         <v>0</v>
       </c>
       <c r="BI116" s="3" t="n">
-        <v>46115.625</v>
+        <v>46115.60416666666</v>
       </c>
     </row>
     <row r="117">
@@ -23403,12 +23403,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23591,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="BI117" s="3" t="n">
-        <v>46115.625</v>
+        <v>46115.60416666666</v>
       </c>
     </row>
     <row r="118">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF129" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26555,12 +26555,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF133" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26743,7 +26743,7 @@
         <v>0</v>
       </c>
       <c r="BI133" s="3" t="n">
-        <v>46115.63541666666</v>
+        <v>46115.625</v>
       </c>
     </row>
     <row r="134">
@@ -26752,12 +26752,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26940,7 +26940,7 @@
         <v>0</v>
       </c>
       <c r="BI134" s="3" t="n">
-        <v>46115.63541666666</v>
+        <v>46115.625</v>
       </c>
     </row>
     <row r="135">
@@ -26949,12 +26949,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF135" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27137,7 +27137,7 @@
         <v>0</v>
       </c>
       <c r="BI135" s="3" t="n">
-        <v>46115.64583333334</v>
+        <v>46115.625</v>
       </c>
     </row>
     <row r="136">
@@ -27146,12 +27146,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF136" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27334,7 +27334,7 @@
         <v>0</v>
       </c>
       <c r="BI136" s="3" t="n">
-        <v>46115.64583333334</v>
+        <v>46115.625</v>
       </c>
     </row>
     <row r="137">
@@ -27343,12 +27343,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27531,7 +27531,7 @@
         <v>0</v>
       </c>
       <c r="BI137" s="3" t="n">
-        <v>46115.64583333334</v>
+        <v>46115.63541666666</v>
       </c>
     </row>
     <row r="138">
@@ -27540,12 +27540,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27728,7 +27728,7 @@
         <v>0</v>
       </c>
       <c r="BI138" s="3" t="n">
-        <v>46115.64583333334</v>
+        <v>46115.63541666666</v>
       </c>
     </row>
     <row r="139">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28328,12 +28328,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28516,7 +28516,7 @@
         <v>0</v>
       </c>
       <c r="BI142" s="3" t="n">
-        <v>46115.65625</v>
+        <v>46115.64583333334</v>
       </c>
     </row>
     <row r="143">
@@ -28525,27 +28525,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28713,7 +28713,7 @@
         <v>0</v>
       </c>
       <c r="BI143" s="3" t="n">
-        <v>46115.65625</v>
+        <v>46115.64583333334</v>
       </c>
     </row>
     <row r="144">
@@ -28722,27 +28722,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28910,7 +28910,7 @@
         <v>0</v>
       </c>
       <c r="BI144" s="3" t="n">
-        <v>46115.65625</v>
+        <v>46115.64583333334</v>
       </c>
     </row>
     <row r="145">
@@ -28919,12 +28919,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29017,16 +29017,16 @@
         <v>0</v>
       </c>
       <c r="AE145" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF145" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG145" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH145" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI145" t="n">
         <v>0</v>
@@ -29107,7 +29107,7 @@
         <v>0</v>
       </c>
       <c r="BI145" s="3" t="n">
-        <v>46115.65625</v>
+        <v>46115.64583333334</v>
       </c>
     </row>
     <row r="146">
@@ -29116,27 +29116,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29304,7 +29304,7 @@
         <v>0</v>
       </c>
       <c r="BI146" s="3" t="n">
-        <v>46115.65625</v>
+        <v>46115.64583333334</v>
       </c>
     </row>
     <row r="147">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30495,27 +30495,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30683,7 +30683,7 @@
         <v>0</v>
       </c>
       <c r="BI153" s="3" t="n">
-        <v>46115.66666666666</v>
+        <v>46115.65625</v>
       </c>
     </row>
     <row r="154">
@@ -30692,7 +30692,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30880,7 +30880,7 @@
         <v>0</v>
       </c>
       <c r="BI154" s="3" t="n">
-        <v>46115.66666666666</v>
+        <v>46115.65625</v>
       </c>
     </row>
     <row r="155">
@@ -30889,27 +30889,27 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30987,10 +30987,10 @@
         <v>0</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF155" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG155" t="n">
         <v>0</v>
@@ -31077,7 +31077,7 @@
         <v>0</v>
       </c>
       <c r="BI155" s="3" t="n">
-        <v>46115.66666666666</v>
+        <v>46115.65625</v>
       </c>
     </row>
     <row r="156">
@@ -31086,12 +31086,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Q156" t="n">
-        <v>6.1</v>
+        <v>5.63</v>
       </c>
       <c r="R156" t="n">
-        <v>14.5</v>
+        <v>10.9</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,16 +31184,16 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AF156" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AG156" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH156" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI156" t="n">
         <v>0</v>
@@ -31274,7 +31274,7 @@
         <v>0</v>
       </c>
       <c r="BI156" s="3" t="n">
-        <v>46115.6875</v>
+        <v>46115.65625</v>
       </c>
     </row>
     <row r="157">
@@ -31283,12 +31283,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,10 +31381,10 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF157" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG157" t="n">
         <v>0</v>
@@ -31471,7 +31471,7 @@
         <v>0</v>
       </c>
       <c r="BI157" s="3" t="n">
-        <v>46115.72916666666</v>
+        <v>46115.65625</v>
       </c>
     </row>
     <row r="158">
@@ -31480,12 +31480,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31668,7 +31668,7 @@
         <v>0</v>
       </c>
       <c r="BI158" s="3" t="n">
-        <v>46115.83333333334</v>
+        <v>46115.66666666666</v>
       </c>
     </row>
     <row r="159">
@@ -31677,27 +31677,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31865,7 +31865,7 @@
         <v>0</v>
       </c>
       <c r="BI159" s="3" t="n">
-        <v>46115.83333333334</v>
+        <v>46115.66666666666</v>
       </c>
     </row>
     <row r="160">
@@ -31874,12 +31874,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF160" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32062,7 +32062,7 @@
         <v>0</v>
       </c>
       <c r="BI160" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.66666666666</v>
       </c>
     </row>
     <row r="161">
@@ -32071,12 +32071,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF161" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32259,7 +32259,7 @@
         <v>0</v>
       </c>
       <c r="BI161" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.6875</v>
       </c>
     </row>
     <row r="162">
@@ -32268,27 +32268,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF162" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -32456,7 +32456,7 @@
         <v>0</v>
       </c>
       <c r="BI162" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.72916666666</v>
       </c>
     </row>
     <row r="163">
@@ -32465,27 +32465,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32653,7 +32653,7 @@
         <v>0</v>
       </c>
       <c r="BI163" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.83333333334</v>
       </c>
     </row>
     <row r="164">
@@ -32662,27 +32662,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32850,7 +32850,7 @@
         <v>0</v>
       </c>
       <c r="BI164" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.83333333334</v>
       </c>
     </row>
     <row r="165">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33745,10 +33745,10 @@
         <v>0</v>
       </c>
       <c r="AE169" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF169" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q170" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -33942,10 +33942,10 @@
         <v>0</v>
       </c>
       <c r="AE170" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF170" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34139,10 +34139,10 @@
         <v>0</v>
       </c>
       <c r="AE171" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF171" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34484,17 +34484,17 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34533,10 +34533,10 @@
         <v>0</v>
       </c>
       <c r="AE173" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF173" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG173" t="n">
         <v>0</v>
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q176" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35321,10 +35321,10 @@
         <v>0</v>
       </c>
       <c r="AE177" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF177" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG177" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36060,7 +36060,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF183" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,22 +36804,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q185" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -36897,10 +36897,10 @@
         <v>0</v>
       </c>
       <c r="AE185" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF185" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG185" t="n">
         <v>0</v>
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,22 +38183,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,22 +38577,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF194" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38966,27 +38966,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39154,7 +39154,7 @@
         <v>0</v>
       </c>
       <c r="BI196" s="3" t="n">
-        <v>46115.89583333334</v>
+        <v>46115.875</v>
       </c>
     </row>
     <row r="197">
@@ -39163,7 +39163,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39351,6 +39351,400 @@
         <v>0</v>
       </c>
       <c r="BI197" s="3" t="n">
+        <v>46115.89583333334</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Gimnasia Jujuy</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Patronato</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N198" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>0</v>
+      </c>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="n">
+        <v>0</v>
+      </c>
+      <c r="T198" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" t="n">
+        <v>0</v>
+      </c>
+      <c r="V198" t="n">
+        <v>0</v>
+      </c>
+      <c r="W198" t="n">
+        <v>0</v>
+      </c>
+      <c r="X198" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI198" s="3" t="n">
+        <v>46115.91666666666</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Chicago Red Stars</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N199" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>0</v>
+      </c>
+      <c r="R199" t="n">
+        <v>0</v>
+      </c>
+      <c r="S199" t="n">
+        <v>0</v>
+      </c>
+      <c r="T199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="n">
+        <v>0</v>
+      </c>
+      <c r="V199" t="n">
+        <v>0</v>
+      </c>
+      <c r="W199" t="n">
+        <v>0</v>
+      </c>
+      <c r="X199" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI199" s="3" t="n">
         <v>46115.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI199"/>
+  <dimension ref="A1:BI201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.36</v>
+        <v>8.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>5.05</v>
       </c>
       <c r="R14" t="n">
-        <v>7.28</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>7.28</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.68</v>
+        <v>1.85</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.18</v>
+        <v>3.64</v>
       </c>
       <c r="R49" t="n">
-        <v>2.6</v>
+        <v>3.96</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.72</v>
+        <v>1.31</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.54</v>
+        <v>5.05</v>
       </c>
       <c r="R57" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.31</v>
+        <v>1.72</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.05</v>
+        <v>3.54</v>
       </c>
       <c r="R58" t="n">
-        <v>9.4</v>
+        <v>4.9</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12962,12 +12962,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>9.07</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>46115.47916666666</v>
+        <v>46115.45833333334</v>
       </c>
     </row>
     <row r="65">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>9.07</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46115.5</v>
+        <v>46115.47916666666</v>
       </c>
     </row>
     <row r="68">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14341,27 +14341,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46115.51041666666</v>
+        <v>46115.5</v>
       </c>
     </row>
     <row r="72">
@@ -14538,27 +14538,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14726,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>46115.52083333334</v>
+        <v>46115.51041666666</v>
       </c>
     </row>
     <row r="73">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15129,27 +15129,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46115.54166666666</v>
+        <v>46115.52083333334</v>
       </c>
     </row>
     <row r="76">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17493,7 +17493,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17681,7 +17681,7 @@
         <v>0</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>46115.55208333334</v>
+        <v>46115.54166666666</v>
       </c>
     </row>
     <row r="88">
@@ -17887,12 +17887,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18075,7 +18075,7 @@
         <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>46115.5625</v>
+        <v>46115.55208333334</v>
       </c>
     </row>
     <row r="90">
@@ -18084,12 +18084,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18272,7 +18272,7 @@
         <v>0</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>46115.57291666666</v>
+        <v>46115.5625</v>
       </c>
     </row>
     <row r="91">
@@ -18281,12 +18281,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46115.57291666666</v>
+        <v>46115.5625</v>
       </c>
     </row>
     <row r="92">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18675,12 +18675,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>46115.58333333334</v>
+        <v>46115.57291666666</v>
       </c>
     </row>
     <row r="94">
@@ -18872,12 +18872,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46115.58333333334</v>
+        <v>46115.57291666666</v>
       </c>
     </row>
     <row r="95">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20842,12 +20842,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21030,7 +21030,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3" t="n">
-        <v>46115.60416666666</v>
+        <v>46115.58333333334</v>
       </c>
     </row>
     <row r="105">
@@ -21039,12 +21039,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21227,7 +21227,7 @@
         <v>0</v>
       </c>
       <c r="BI105" s="3" t="n">
-        <v>46115.60416666666</v>
+        <v>46115.58333333334</v>
       </c>
     </row>
     <row r="106">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF116" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23600,12 +23600,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23788,7 +23788,7 @@
         <v>0</v>
       </c>
       <c r="BI118" s="3" t="n">
-        <v>46115.625</v>
+        <v>46115.60416666666</v>
       </c>
     </row>
     <row r="119">
@@ -23797,12 +23797,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23846,7 +23846,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="BI119" s="3" t="n">
-        <v>46115.625</v>
+        <v>46115.60416666666</v>
       </c>
     </row>
     <row r="120">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF127" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>2.71</v>
+        <v>1.99</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.26</v>
+        <v>3.65</v>
       </c>
       <c r="R131" t="n">
-        <v>2.52</v>
+        <v>3.44</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF133" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF136" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27343,12 +27343,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27531,7 +27531,7 @@
         <v>0</v>
       </c>
       <c r="BI137" s="3" t="n">
-        <v>46115.63541666666</v>
+        <v>46115.625</v>
       </c>
     </row>
     <row r="138">
@@ -27540,12 +27540,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27728,7 +27728,7 @@
         <v>0</v>
       </c>
       <c r="BI138" s="3" t="n">
-        <v>46115.63541666666</v>
+        <v>46115.625</v>
       </c>
     </row>
     <row r="139">
@@ -27737,12 +27737,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27925,7 +27925,7 @@
         <v>0</v>
       </c>
       <c r="BI139" s="3" t="n">
-        <v>46115.64583333334</v>
+        <v>46115.63541666666</v>
       </c>
     </row>
     <row r="140">
@@ -27934,12 +27934,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28122,7 +28122,7 @@
         <v>0</v>
       </c>
       <c r="BI140" s="3" t="n">
-        <v>46115.64583333334</v>
+        <v>46115.63541666666</v>
       </c>
     </row>
     <row r="141">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29313,27 +29313,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29501,7 +29501,7 @@
         <v>0</v>
       </c>
       <c r="BI147" s="3" t="n">
-        <v>46115.65625</v>
+        <v>46115.64583333334</v>
       </c>
     </row>
     <row r="148">
@@ -29510,27 +29510,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29698,7 +29698,7 @@
         <v>0</v>
       </c>
       <c r="BI148" s="3" t="n">
-        <v>46115.65625</v>
+        <v>46115.64583333334</v>
       </c>
     </row>
     <row r="149">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,16 +30790,16 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF154" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG154" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH154" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI154" t="n">
         <v>0</v>
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,16 +31184,16 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF156" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG156" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH156" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI156" t="n">
         <v>0</v>
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31668,7 +31668,7 @@
         <v>0</v>
       </c>
       <c r="BI158" s="3" t="n">
-        <v>46115.66666666666</v>
+        <v>46115.65625</v>
       </c>
     </row>
     <row r="159">
@@ -31677,27 +31677,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31865,7 +31865,7 @@
         <v>0</v>
       </c>
       <c r="BI159" s="3" t="n">
-        <v>46115.66666666666</v>
+        <v>46115.65625</v>
       </c>
     </row>
     <row r="160">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF160" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32071,27 +32071,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF161" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32259,7 +32259,7 @@
         <v>0</v>
       </c>
       <c r="BI161" s="3" t="n">
-        <v>46115.6875</v>
+        <v>46115.66666666666</v>
       </c>
     </row>
     <row r="162">
@@ -32268,27 +32268,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="R162" t="n">
-        <v>7.15</v>
+        <v>6.46</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AF162" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -32456,7 +32456,7 @@
         <v>0</v>
       </c>
       <c r="BI162" s="3" t="n">
-        <v>46115.72916666666</v>
+        <v>46115.66666666666</v>
       </c>
     </row>
     <row r="163">
@@ -32465,27 +32465,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32563,10 +32563,10 @@
         <v>0</v>
       </c>
       <c r="AE163" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF163" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG163" t="n">
         <v>0</v>
@@ -32653,7 +32653,7 @@
         <v>0</v>
       </c>
       <c r="BI163" s="3" t="n">
-        <v>46115.83333333334</v>
+        <v>46115.6875</v>
       </c>
     </row>
     <row r="164">
@@ -32662,12 +32662,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q164" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R164" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32760,10 +32760,10 @@
         <v>0</v>
       </c>
       <c r="AE164" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF164" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG164" t="n">
         <v>0</v>
@@ -32850,7 +32850,7 @@
         <v>0</v>
       </c>
       <c r="BI164" s="3" t="n">
-        <v>46115.83333333334</v>
+        <v>46115.72916666666</v>
       </c>
     </row>
     <row r="165">
@@ -32859,27 +32859,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33047,7 +33047,7 @@
         <v>0</v>
       </c>
       <c r="BI165" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.83333333334</v>
       </c>
     </row>
     <row r="166">
@@ -33056,27 +33056,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33244,7 +33244,7 @@
         <v>0</v>
       </c>
       <c r="BI166" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.83333333334</v>
       </c>
     </row>
     <row r="167">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,22 +33652,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33745,10 +33745,10 @@
         <v>0</v>
       </c>
       <c r="AE169" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF169" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -33942,10 +33942,10 @@
         <v>0</v>
       </c>
       <c r="AE170" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF170" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG170" t="n">
         <v>0</v>
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34287,7 +34287,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34533,10 +34533,10 @@
         <v>0</v>
       </c>
       <c r="AE173" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF173" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34878,7 +34878,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q176" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35321,10 +35321,10 @@
         <v>0</v>
       </c>
       <c r="AE177" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF177" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG177" t="n">
         <v>0</v>
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36060,17 +36060,17 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF183" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37291,10 +37291,10 @@
         <v>0</v>
       </c>
       <c r="AE187" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF187" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG187" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q190" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37882,10 +37882,10 @@
         <v>0</v>
       </c>
       <c r="AE190" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF190" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG190" t="n">
         <v>0</v>
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,22 +38183,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,22 +38577,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF195" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39163,27 +39163,27 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39351,7 +39351,7 @@
         <v>0</v>
       </c>
       <c r="BI197" s="3" t="n">
-        <v>46115.89583333334</v>
+        <v>46115.875</v>
       </c>
     </row>
     <row r="198">
@@ -39360,27 +39360,27 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39409,7 +39409,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -39548,7 +39548,7 @@
         <v>0</v>
       </c>
       <c r="BI198" s="3" t="n">
-        <v>46115.91666666666</v>
+        <v>46115.875</v>
       </c>
     </row>
     <row r="199">
@@ -39557,7 +39557,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39745,6 +39745,400 @@
         <v>0</v>
       </c>
       <c r="BI199" s="3" t="n">
+        <v>46115.89583333334</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Chicago Red Stars</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N200" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>0</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="n">
+        <v>0</v>
+      </c>
+      <c r="T200" t="n">
+        <v>0</v>
+      </c>
+      <c r="U200" t="n">
+        <v>0</v>
+      </c>
+      <c r="V200" t="n">
+        <v>0</v>
+      </c>
+      <c r="W200" t="n">
+        <v>0</v>
+      </c>
+      <c r="X200" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI200" s="3" t="n">
+        <v>46115.91666666666</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Gimnasia Jujuy</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Patronato</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N201" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>0</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="S201" t="n">
+        <v>0</v>
+      </c>
+      <c r="T201" t="n">
+        <v>0</v>
+      </c>
+      <c r="U201" t="n">
+        <v>0</v>
+      </c>
+      <c r="V201" t="n">
+        <v>0</v>
+      </c>
+      <c r="W201" t="n">
+        <v>0</v>
+      </c>
+      <c r="X201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI201" s="3" t="n">
         <v>46115.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>8.75</v>
+        <v>1.36</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.05</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>7.28</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="R16" t="n">
-        <v>7.28</v>
+        <v>4.75</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R46" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9517,7 +9517,7 @@
         <v>2.05</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.85</v>
+        <v>2.68</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.64</v>
+        <v>3.18</v>
       </c>
       <c r="R49" t="n">
-        <v>3.96</v>
+        <v>2.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.79</v>
+        <v>7.55</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.65</v>
+        <v>4.65</v>
       </c>
       <c r="R54" t="n">
-        <v>4.27</v>
+        <v>1.33</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>9.07</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>9.07</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,139 +17743,139 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI88" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ88" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL88" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO88" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AS88" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AT88" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AU88" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AV88" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AW88" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AY88" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AZ88" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BA88" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BB88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC88" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD88" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE88" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF88" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG88" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BH88" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BI88" s="3" t="n">
         <v>46115.55208333334</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,139 +17940,139 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI89" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL89" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP89" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR89" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AS89" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AU89" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AV89" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW89" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AY89" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ89" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BA89" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BB89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC89" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD89" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE89" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF89" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG89" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BH89" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BI89" s="3" t="n">
         <v>46115.55208333334</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23255,17 +23255,17 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23846,7 +23846,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF121" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF125" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF129" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26259,10 +26259,10 @@
         <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF131" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF132" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,16 +30790,16 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF154" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG154" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH154" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI154" t="n">
         <v>0</v>
@@ -30894,22 +30894,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,16 +31381,16 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF157" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG157" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH157" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF160" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF162" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,22 +33652,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q170" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -33942,10 +33942,10 @@
         <v>0</v>
       </c>
       <c r="AE170" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF170" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG170" t="n">
         <v>0</v>
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34090,7 +34090,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34287,7 +34287,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34533,10 +34533,10 @@
         <v>0</v>
       </c>
       <c r="AE173" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF173" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG173" t="n">
         <v>0</v>
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF183" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36651,7 +36651,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37291,10 +37291,10 @@
         <v>0</v>
       </c>
       <c r="AE187" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF187" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG187" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q188" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF188" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37882,10 +37882,10 @@
         <v>0</v>
       </c>
       <c r="AE190" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF190" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG190" t="n">
         <v>0</v>
@@ -38183,22 +38183,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38276,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AE192" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF192" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -38380,22 +38380,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF195" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39409,7 +39409,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39803,7 +39803,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40000,7 +40000,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P201" t="n">

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.61</v>
+        <v>3.88</v>
       </c>
       <c r="R17" t="n">
-        <v>2.84</v>
+        <v>4.75</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.76</v>
+        <v>7.55</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.54</v>
+        <v>4.65</v>
       </c>
       <c r="R41" t="n">
-        <v>4.61</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.79</v>
+        <v>2.43</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="R43" t="n">
-        <v>4.27</v>
+        <v>2.63</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.4</v>
+        <v>1.12</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="R46" t="n">
-        <v>2.96</v>
+        <v>19</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23255,7 +23255,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.99</v>
+        <v>2.71</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.65</v>
+        <v>3.26</v>
       </c>
       <c r="R121" t="n">
-        <v>3.44</v>
+        <v>2.52</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF122" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.47</v>
+        <v>1.72</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.18</v>
+        <v>3.7</v>
       </c>
       <c r="R125" t="n">
-        <v>2.84</v>
+        <v>4.65</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AF125" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R127" t="n">
-        <v>4.65</v>
+        <v>3.44</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AF127" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF160" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF161" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33745,10 +33745,10 @@
         <v>0</v>
       </c>
       <c r="AE169" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF169" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -33942,10 +33942,10 @@
         <v>0</v>
       </c>
       <c r="AE170" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF170" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34090,7 +34090,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34533,10 +34533,10 @@
         <v>0</v>
       </c>
       <c r="AE173" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF173" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG173" t="n">
         <v>0</v>
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q180" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -35912,10 +35912,10 @@
         <v>0</v>
       </c>
       <c r="AE180" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF180" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36651,7 +36651,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF188" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q190" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37882,10 +37882,10 @@
         <v>0</v>
       </c>
       <c r="AE190" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF190" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG190" t="n">
         <v>0</v>
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,22 +38183,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38227,17 +38227,17 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P192" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38276,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AE192" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF192" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -38380,22 +38380,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q193" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R193" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38818,7 +38818,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q197" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39261,10 +39261,10 @@
         <v>0</v>
       </c>
       <c r="AE197" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF197" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39803,7 +39803,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40000,7 +40000,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P201" t="n">

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.68</v>
+        <v>7.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.18</v>
+        <v>4.65</v>
       </c>
       <c r="R36" t="n">
-        <v>2.6</v>
+        <v>1.33</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.76</v>
+        <v>2.68</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.54</v>
+        <v>3.18</v>
       </c>
       <c r="R37" t="n">
-        <v>4.61</v>
+        <v>2.6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.12</v>
+        <v>1.85</v>
       </c>
       <c r="Q46" t="n">
-        <v>7.5</v>
+        <v>3.64</v>
       </c>
       <c r="R46" t="n">
-        <v>19</v>
+        <v>3.96</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.33</v>
+        <v>3.65</v>
       </c>
       <c r="R63" t="n">
-        <v>6.4</v>
+        <v>4.27</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>9.07</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>9.07</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,139 +17743,139 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V88" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI88" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL88" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP88" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR88" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AS88" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AU88" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AV88" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW88" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AY88" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BA88" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BB88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC88" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD88" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE88" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF88" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG88" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BH88" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BI88" s="3" t="n">
         <v>46115.55208333334</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,139 +17940,139 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI89" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ89" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL89" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM89" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN89" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO89" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AR89" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AS89" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AT89" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AU89" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AV89" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AW89" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX89" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AY89" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AZ89" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BA89" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BB89" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC89" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD89" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE89" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF89" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG89" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BH89" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
         <v>46115.55208333334</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF117" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.71</v>
+        <v>2.47</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="R121" t="n">
-        <v>2.52</v>
+        <v>2.84</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24292,7 +24292,7 @@
         <v>2.05</v>
       </c>
       <c r="AF121" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF122" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="R125" t="n">
-        <v>4.65</v>
+        <v>3.87</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AF125" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF127" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q152" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF161" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF162" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33745,10 +33745,10 @@
         <v>0</v>
       </c>
       <c r="AE169" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF169" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34484,7 +34484,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q180" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -35912,10 +35912,10 @@
         <v>0</v>
       </c>
       <c r="AE180" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF180" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36109,10 +36109,10 @@
         <v>0</v>
       </c>
       <c r="AE181" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF181" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG181" t="n">
         <v>0</v>
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF183" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36848,7 +36848,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q189" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R189" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37685,10 +37685,10 @@
         <v>0</v>
       </c>
       <c r="AE189" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF189" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG189" t="n">
         <v>0</v>
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37882,10 +37882,10 @@
         <v>0</v>
       </c>
       <c r="AE190" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF190" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG190" t="n">
         <v>0</v>
@@ -37986,22 +37986,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q191" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38079,10 +38079,10 @@
         <v>0</v>
       </c>
       <c r="AE191" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF191" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG191" t="n">
         <v>0</v>
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38227,7 +38227,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P192" t="n">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q193" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38818,7 +38818,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39261,10 +39261,10 @@
         <v>0</v>
       </c>
       <c r="AE197" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF197" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G198" t="n">

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.72</v>
+        <v>3.15</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.54</v>
+        <v>3.08</v>
       </c>
       <c r="R31" t="n">
-        <v>4.9</v>
+        <v>2.35</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.12</v>
+        <v>2.68</v>
       </c>
       <c r="Q33" t="n">
-        <v>7.5</v>
+        <v>3.22</v>
       </c>
       <c r="R33" t="n">
-        <v>19</v>
+        <v>2.57</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="R35" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>7.55</v>
+        <v>1.76</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.65</v>
+        <v>3.54</v>
       </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>4.61</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="R42" t="n">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="R59" t="n">
-        <v>6.4</v>
+        <v>5.32</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22270,7 +22270,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF117" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF121" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF122" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="R125" t="n">
-        <v>3.87</v>
+        <v>4.65</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AF125" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>2.71</v>
+        <v>1.9</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.26</v>
+        <v>3.54</v>
       </c>
       <c r="R126" t="n">
-        <v>2.52</v>
+        <v>3.87</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AF126" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF127" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF149" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="R152" t="n">
-        <v>2.3</v>
+        <v>4.04</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF153" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,10 +30790,10 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF154" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG154" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>7.28</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,10 +31184,10 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF156" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG156" t="n">
         <v>0</v>
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.34</v>
+        <v>2.91</v>
       </c>
       <c r="Q157" t="n">
-        <v>5.63</v>
+        <v>3.2</v>
       </c>
       <c r="R157" t="n">
-        <v>10.9</v>
+        <v>2.26</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,16 +31381,16 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF157" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,16 +31578,16 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF158" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG158" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH158" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF160" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>1.47</v>
+        <v>3.29</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="R162" t="n">
-        <v>6.46</v>
+        <v>2.18</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF162" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33302,7 +33302,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34484,7 +34484,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36109,10 +36109,10 @@
         <v>0</v>
       </c>
       <c r="AE181" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF181" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG181" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36306,10 +36306,10 @@
         <v>0</v>
       </c>
       <c r="AE182" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF182" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG182" t="n">
         <v>0</v>
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,22 +36804,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36848,7 +36848,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37045,7 +37045,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q188" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF188" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>1.66</v>
+        <v>2.26</v>
       </c>
       <c r="Q189" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="R189" t="n">
-        <v>5.23</v>
+        <v>3.2</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37685,10 +37685,10 @@
         <v>0</v>
       </c>
       <c r="AE189" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF189" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG189" t="n">
         <v>0</v>
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39803,7 +39803,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40000,7 +40000,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P201" t="n">

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI201"/>
+  <dimension ref="A1:BI198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.17</v>
+        <v>1.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.61</v>
+        <v>4.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.84</v>
+        <v>7.28</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.36</v>
+        <v>8.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>5.05</v>
       </c>
       <c r="R14" t="n">
-        <v>7.28</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>8.75</v>
+        <v>2.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.05</v>
+        <v>3.61</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>2.84</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.68</v>
+        <v>1.76</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.22</v>
+        <v>3.54</v>
       </c>
       <c r="R33" t="n">
-        <v>2.57</v>
+        <v>4.61</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.68</v>
+        <v>1.47</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.18</v>
+        <v>4.33</v>
       </c>
       <c r="R35" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.43</v>
+        <v>1.64</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="R42" t="n">
-        <v>2.63</v>
+        <v>4.5</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.54</v>
+        <v>4.15</v>
       </c>
       <c r="R45" t="n">
-        <v>4.9</v>
+        <v>5.32</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.31</v>
+        <v>1.72</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.05</v>
+        <v>3.54</v>
       </c>
       <c r="R57" t="n">
-        <v>9.4</v>
+        <v>4.9</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="R58" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>9.07</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>9.07</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,139 +17743,139 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI88" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ88" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL88" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO88" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AS88" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AT88" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AU88" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AV88" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AW88" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AY88" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AZ88" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BA88" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BB88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC88" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD88" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE88" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF88" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG88" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BH88" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BI88" s="3" t="n">
         <v>46115.55208333334</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,139 +17940,139 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI89" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL89" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP89" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR89" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AS89" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AU89" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AV89" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW89" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AY89" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ89" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BA89" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BB89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC89" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD89" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE89" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF89" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG89" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BH89" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BI89" s="3" t="n">
         <v>46115.55208333334</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF107" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22270,7 +22270,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="R122" t="n">
-        <v>3.44</v>
+        <v>4.65</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AF122" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF127" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26259,10 +26259,10 @@
         <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF131" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF134" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF135" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF137" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF149" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,16 +30002,16 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF150" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG150" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH150" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>3</v>
+        <v>1.39</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="R151" t="n">
-        <v>2.3</v>
+        <v>7.28</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF151" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1.88</v>
+        <v>3.99</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="R152" t="n">
-        <v>4.04</v>
+        <v>1.92</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.2</v>
+        <v>5.35</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="R153" t="n">
-        <v>2.89</v>
+        <v>1.58</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AF153" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>5.35</v>
+        <v>1.88</v>
       </c>
       <c r="Q154" t="n">
-        <v>4.05</v>
+        <v>3.48</v>
       </c>
       <c r="R154" t="n">
-        <v>1.58</v>
+        <v>4.04</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,10 +30790,10 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF154" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG154" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>3.99</v>
+        <v>2.28</v>
       </c>
       <c r="Q155" t="n">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="R155" t="n">
-        <v>1.92</v>
+        <v>2.58</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30987,10 +30987,10 @@
         <v>0</v>
       </c>
       <c r="AE155" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF155" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG155" t="n">
         <v>0</v>
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>1.39</v>
+        <v>3</v>
       </c>
       <c r="Q156" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="R156" t="n">
-        <v>7.28</v>
+        <v>2.3</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,10 +31184,10 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF156" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG156" t="n">
         <v>0</v>
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>1.34</v>
+        <v>2.2</v>
       </c>
       <c r="Q158" t="n">
-        <v>5.63</v>
+        <v>3.35</v>
       </c>
       <c r="R158" t="n">
-        <v>10.9</v>
+        <v>2.89</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,16 +31578,16 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AF158" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AG158" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH158" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI158" t="n">
         <v>0</v>
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>1.47</v>
+        <v>3.29</v>
       </c>
       <c r="Q160" t="n">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="R160" t="n">
-        <v>6.46</v>
+        <v>2.18</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF160" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF161" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33302,7 +33302,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36306,10 +36306,10 @@
         <v>0</v>
       </c>
       <c r="AE182" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF182" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF183" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,22 +36804,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37045,17 +37045,17 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37094,10 +37094,10 @@
         <v>0</v>
       </c>
       <c r="AE186" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF186" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG186" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37242,7 +37242,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37488,10 +37488,10 @@
         <v>0</v>
       </c>
       <c r="AE188" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF188" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q189" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37789,22 +37789,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,22 +37986,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="Q191" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="R191" t="n">
-        <v>4.98</v>
+        <v>3</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38079,10 +38079,10 @@
         <v>0</v>
       </c>
       <c r="AE191" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AF191" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG191" t="n">
         <v>0</v>
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q193" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R193" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38473,10 +38473,10 @@
         <v>0</v>
       </c>
       <c r="AE193" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF193" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG193" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF194" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38818,7 +38818,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -38966,27 +38966,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39154,7 +39154,7 @@
         <v>0</v>
       </c>
       <c r="BI196" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.89583333334</v>
       </c>
     </row>
     <row r="197">
@@ -39163,27 +39163,27 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39351,7 +39351,7 @@
         <v>0</v>
       </c>
       <c r="BI197" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.91666666666</v>
       </c>
     </row>
     <row r="198">
@@ -39360,27 +39360,27 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39548,597 +39548,6 @@
         <v>0</v>
       </c>
       <c r="BI198" s="3" t="n">
-        <v>46115.875</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Houston Dash</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="G199" t="n">
-        <v>0</v>
-      </c>
-      <c r="H199" t="n">
-        <v>0</v>
-      </c>
-      <c r="I199" t="n">
-        <v>0</v>
-      </c>
-      <c r="J199" t="n">
-        <v>0</v>
-      </c>
-      <c r="K199" t="n">
-        <v>0</v>
-      </c>
-      <c r="L199" t="n">
-        <v>0</v>
-      </c>
-      <c r="M199" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N199" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P199" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
-      <c r="R199" t="n">
-        <v>0</v>
-      </c>
-      <c r="S199" t="n">
-        <v>0</v>
-      </c>
-      <c r="T199" t="n">
-        <v>0</v>
-      </c>
-      <c r="U199" t="n">
-        <v>0</v>
-      </c>
-      <c r="V199" t="n">
-        <v>0</v>
-      </c>
-      <c r="W199" t="n">
-        <v>0</v>
-      </c>
-      <c r="X199" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y199" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI199" s="3" t="n">
-        <v>46115.89583333334</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Gimnasia Jujuy</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>Patronato</t>
-        </is>
-      </c>
-      <c r="G200" t="n">
-        <v>0</v>
-      </c>
-      <c r="H200" t="n">
-        <v>0</v>
-      </c>
-      <c r="I200" t="n">
-        <v>0</v>
-      </c>
-      <c r="J200" t="n">
-        <v>0</v>
-      </c>
-      <c r="K200" t="n">
-        <v>0</v>
-      </c>
-      <c r="L200" t="n">
-        <v>0</v>
-      </c>
-      <c r="M200" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N200" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O200" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="P200" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
-      <c r="R200" t="n">
-        <v>0</v>
-      </c>
-      <c r="S200" t="n">
-        <v>0</v>
-      </c>
-      <c r="T200" t="n">
-        <v>0</v>
-      </c>
-      <c r="U200" t="n">
-        <v>0</v>
-      </c>
-      <c r="V200" t="n">
-        <v>0</v>
-      </c>
-      <c r="W200" t="n">
-        <v>0</v>
-      </c>
-      <c r="X200" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y200" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ200" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA200" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB200" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC200" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD200" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE200" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF200" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG200" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH200" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI200" s="3" t="n">
-        <v>46115.91666666666</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>Chicago Red Stars</t>
-        </is>
-      </c>
-      <c r="G201" t="n">
-        <v>0</v>
-      </c>
-      <c r="H201" t="n">
-        <v>0</v>
-      </c>
-      <c r="I201" t="n">
-        <v>0</v>
-      </c>
-      <c r="J201" t="n">
-        <v>0</v>
-      </c>
-      <c r="K201" t="n">
-        <v>0</v>
-      </c>
-      <c r="L201" t="n">
-        <v>0</v>
-      </c>
-      <c r="M201" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N201" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O201" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P201" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
-      <c r="R201" t="n">
-        <v>0</v>
-      </c>
-      <c r="S201" t="n">
-        <v>0</v>
-      </c>
-      <c r="T201" t="n">
-        <v>0</v>
-      </c>
-      <c r="U201" t="n">
-        <v>0</v>
-      </c>
-      <c r="V201" t="n">
-        <v>0</v>
-      </c>
-      <c r="W201" t="n">
-        <v>0</v>
-      </c>
-      <c r="X201" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y201" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ201" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA201" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB201" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC201" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD201" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE201" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF201" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG201" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH201" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI201" s="3" t="n">
         <v>46115.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI198"/>
+  <dimension ref="A1:BI192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>7.28</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>8.75</v>
+        <v>2.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.05</v>
+        <v>3.61</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>2.84</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.17</v>
+        <v>8.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.61</v>
+        <v>5.05</v>
       </c>
       <c r="R15" t="n">
-        <v>2.84</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="R16" t="n">
-        <v>4.75</v>
+        <v>7.28</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46115.45138888889</v>
+        <v>46115.45833333334</v>
       </c>
     </row>
     <row r="31">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="Q43" t="n">
-        <v>7.5</v>
+        <v>4.15</v>
       </c>
       <c r="R43" t="n">
-        <v>19</v>
+        <v>5.32</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.55</v>
+        <v>2.64</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.15</v>
+        <v>3.22</v>
       </c>
       <c r="R45" t="n">
-        <v>5.32</v>
+        <v>2.61</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R47" t="n">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.08</v>
+        <v>3.54</v>
       </c>
       <c r="R48" t="n">
-        <v>2.35</v>
+        <v>4.9</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.79</v>
+        <v>1.31</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.65</v>
+        <v>5.05</v>
       </c>
       <c r="R53" t="n">
-        <v>4.27</v>
+        <v>9.4</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="R54" t="n">
-        <v>3.96</v>
+        <v>4.27</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="Q56" t="n">
         <v>3.22</v>
       </c>
       <c r="R56" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.72</v>
+        <v>2.68</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.54</v>
+        <v>3.18</v>
       </c>
       <c r="R57" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="Q61" t="n">
-        <v>5.05</v>
+        <v>4.33</v>
       </c>
       <c r="R61" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.68</v>
+        <v>1.64</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.22</v>
+        <v>4.25</v>
       </c>
       <c r="R63" t="n">
-        <v>2.57</v>
+        <v>4.5</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12962,12 +12962,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>9.07</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>46115.45833333334</v>
+        <v>46115.47916666666</v>
       </c>
     </row>
     <row r="65">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>9.07</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13553,12 +13553,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46115.47916666666</v>
+        <v>46115.5</v>
       </c>
     </row>
     <row r="68">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14341,27 +14341,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46115.5</v>
+        <v>46115.51041666666</v>
       </c>
     </row>
     <row r="72">
@@ -14538,27 +14538,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14726,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>46115.51041666666</v>
+        <v>46115.52083333334</v>
       </c>
     </row>
     <row r="73">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46115.52083333334</v>
+        <v>46115.54166666666</v>
       </c>
     </row>
     <row r="76">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17493,12 +17493,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17681,7 +17681,7 @@
         <v>0</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>46115.54166666666</v>
+        <v>46115.55208333334</v>
       </c>
     </row>
     <row r="88">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,139 +17743,139 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V88" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI88" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL88" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO88" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP88" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR88" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AS88" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AU88" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AV88" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW88" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AY88" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BA88" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BB88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC88" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD88" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE88" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF88" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG88" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BH88" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BI88" s="3" t="n">
         <v>46115.55208333334</v>
@@ -17887,12 +17887,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,142 +17940,142 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI89" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ89" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL89" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM89" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN89" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO89" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AR89" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AS89" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AT89" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AU89" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AV89" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AW89" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX89" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AY89" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AZ89" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BA89" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BB89" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC89" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD89" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE89" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF89" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG89" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BH89" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>46115.55208333334</v>
+        <v>46115.5625</v>
       </c>
     </row>
     <row r="90">
@@ -18084,12 +18084,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18272,7 +18272,7 @@
         <v>0</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>46115.5625</v>
+        <v>46115.57291666666</v>
       </c>
     </row>
     <row r="91">
@@ -18281,12 +18281,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46115.5625</v>
+        <v>46115.57291666666</v>
       </c>
     </row>
     <row r="92">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18675,12 +18675,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>46115.57291666666</v>
+        <v>46115.58333333334</v>
       </c>
     </row>
     <row r="94">
@@ -18872,12 +18872,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46115.57291666666</v>
+        <v>46115.58333333334</v>
       </c>
     </row>
     <row r="95">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20842,12 +20842,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21030,7 +21030,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3" t="n">
-        <v>46115.58333333334</v>
+        <v>46115.60416666666</v>
       </c>
     </row>
     <row r="105">
@@ -21039,12 +21039,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21227,7 +21227,7 @@
         <v>0</v>
       </c>
       <c r="BI105" s="3" t="n">
-        <v>46115.58333333334</v>
+        <v>46115.60416666666</v>
       </c>
     </row>
     <row r="106">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23788,7 +23788,7 @@
         <v>0</v>
       </c>
       <c r="BI118" s="3" t="n">
-        <v>46115.60416666666</v>
+        <v>46115.625</v>
       </c>
     </row>
     <row r="119">
@@ -23797,12 +23797,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>3.56</v>
+        <v>1.36</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.2</v>
+        <v>4.65</v>
       </c>
       <c r="R119" t="n">
-        <v>2.09</v>
+        <v>6.69</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="BI119" s="3" t="n">
-        <v>46115.60416666666</v>
+        <v>46115.625</v>
       </c>
     </row>
     <row r="120">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF122" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26259,10 +26259,10 @@
         <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF131" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF133" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>2.71</v>
+        <v>1.99</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.26</v>
+        <v>3.65</v>
       </c>
       <c r="R134" t="n">
-        <v>2.52</v>
+        <v>3.44</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.9</v>
+        <v>2.47</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.54</v>
+        <v>3.18</v>
       </c>
       <c r="R135" t="n">
-        <v>3.87</v>
+        <v>2.84</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF136" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27343,12 +27343,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF137" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27531,7 +27531,7 @@
         <v>0</v>
       </c>
       <c r="BI137" s="3" t="n">
-        <v>46115.625</v>
+        <v>46115.63541666666</v>
       </c>
     </row>
     <row r="138">
@@ -27540,12 +27540,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27728,7 +27728,7 @@
         <v>0</v>
       </c>
       <c r="BI138" s="3" t="n">
-        <v>46115.625</v>
+        <v>46115.63541666666</v>
       </c>
     </row>
     <row r="139">
@@ -27737,12 +27737,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27925,7 +27925,7 @@
         <v>0</v>
       </c>
       <c r="BI139" s="3" t="n">
-        <v>46115.63541666666</v>
+        <v>46115.64583333334</v>
       </c>
     </row>
     <row r="140">
@@ -27934,12 +27934,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28122,7 +28122,7 @@
         <v>0</v>
       </c>
       <c r="BI140" s="3" t="n">
-        <v>46115.63541666666</v>
+        <v>46115.64583333334</v>
       </c>
     </row>
     <row r="141">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29313,27 +29313,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29501,7 +29501,7 @@
         <v>0</v>
       </c>
       <c r="BI147" s="3" t="n">
-        <v>46115.64583333334</v>
+        <v>46115.65625</v>
       </c>
     </row>
     <row r="148">
@@ -29510,27 +29510,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29698,7 +29698,7 @@
         <v>0</v>
       </c>
       <c r="BI148" s="3" t="n">
-        <v>46115.64583333334</v>
+        <v>46115.65625</v>
       </c>
     </row>
     <row r="149">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF149" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>1.34</v>
+        <v>3.99</v>
       </c>
       <c r="Q150" t="n">
-        <v>5.63</v>
+        <v>3.38</v>
       </c>
       <c r="R150" t="n">
-        <v>10.9</v>
+        <v>1.92</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,16 +30002,16 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF150" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG150" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH150" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>1.39</v>
+        <v>3</v>
       </c>
       <c r="Q151" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="R151" t="n">
-        <v>7.28</v>
+        <v>2.3</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF151" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,55 +30351,55 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>3.99</v>
+        <v>2.2</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="R152" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="S152" t="n">
+        <v>0</v>
+      </c>
+      <c r="T152" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" t="n">
+        <v>0</v>
+      </c>
+      <c r="V152" t="n">
+        <v>0</v>
+      </c>
+      <c r="W152" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF152" t="n">
         <v>1.92</v>
-      </c>
-      <c r="S152" t="n">
-        <v>0</v>
-      </c>
-      <c r="T152" t="n">
-        <v>0</v>
-      </c>
-      <c r="U152" t="n">
-        <v>0</v>
-      </c>
-      <c r="V152" t="n">
-        <v>0</v>
-      </c>
-      <c r="W152" t="n">
-        <v>0</v>
-      </c>
-      <c r="X152" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y152" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF152" t="n">
-        <v>0</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF153" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="R154" t="n">
-        <v>4.04</v>
+        <v>2.58</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,10 +30790,10 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF154" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG154" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>2.28</v>
+        <v>1.39</v>
       </c>
       <c r="Q155" t="n">
-        <v>3.52</v>
+        <v>4.75</v>
       </c>
       <c r="R155" t="n">
-        <v>2.58</v>
+        <v>7.28</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30987,10 +30987,10 @@
         <v>0</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AF155" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AG155" t="n">
         <v>0</v>
@@ -31091,22 +31091,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="R156" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.91</v>
+        <v>1.34</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.2</v>
+        <v>5.63</v>
       </c>
       <c r="R157" t="n">
-        <v>2.26</v>
+        <v>10.9</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,16 +31381,16 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF157" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG157" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH157" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -31480,27 +31480,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF158" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG158" t="n">
         <v>0</v>
@@ -31668,7 +31668,7 @@
         <v>0</v>
       </c>
       <c r="BI158" s="3" t="n">
-        <v>46115.65625</v>
+        <v>46115.66666666666</v>
       </c>
     </row>
     <row r="159">
@@ -31677,12 +31677,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31865,7 +31865,7 @@
         <v>0</v>
       </c>
       <c r="BI159" s="3" t="n">
-        <v>46115.65625</v>
+        <v>46115.66666666666</v>
       </c>
     </row>
     <row r="160">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>3.29</v>
+        <v>1.47</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.28</v>
+        <v>4.3</v>
       </c>
       <c r="R160" t="n">
-        <v>2.18</v>
+        <v>6.46</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF160" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32071,12 +32071,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="Q161" t="n">
-        <v>4.3</v>
+        <v>6.1</v>
       </c>
       <c r="R161" t="n">
-        <v>6.46</v>
+        <v>14.5</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AF161" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32259,7 +32259,7 @@
         <v>0</v>
       </c>
       <c r="BI161" s="3" t="n">
-        <v>46115.66666666666</v>
+        <v>46115.6875</v>
       </c>
     </row>
     <row r="162">
@@ -32268,27 +32268,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF162" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -32456,7 +32456,7 @@
         <v>0</v>
       </c>
       <c r="BI162" s="3" t="n">
-        <v>46115.66666666666</v>
+        <v>46115.72916666666</v>
       </c>
     </row>
     <row r="163">
@@ -32465,27 +32465,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q163" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32563,10 +32563,10 @@
         <v>0</v>
       </c>
       <c r="AE163" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF163" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG163" t="n">
         <v>0</v>
@@ -32653,7 +32653,7 @@
         <v>0</v>
       </c>
       <c r="BI163" s="3" t="n">
-        <v>46115.6875</v>
+        <v>46115.83333333334</v>
       </c>
     </row>
     <row r="164">
@@ -32662,7 +32662,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q164" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32760,10 +32760,10 @@
         <v>0</v>
       </c>
       <c r="AE164" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF164" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG164" t="n">
         <v>0</v>
@@ -32850,7 +32850,7 @@
         <v>0</v>
       </c>
       <c r="BI164" s="3" t="n">
-        <v>46115.72916666666</v>
+        <v>46115.83333333334</v>
       </c>
     </row>
     <row r="165">
@@ -32859,27 +32859,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33047,7 +33047,7 @@
         <v>0</v>
       </c>
       <c r="BI165" s="3" t="n">
-        <v>46115.83333333334</v>
+        <v>46115.875</v>
       </c>
     </row>
     <row r="166">
@@ -33056,27 +33056,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33244,7 +33244,7 @@
         <v>0</v>
       </c>
       <c r="BI166" s="3" t="n">
-        <v>46115.83333333334</v>
+        <v>46115.875</v>
       </c>
     </row>
     <row r="167">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34730,10 +34730,10 @@
         <v>0</v>
       </c>
       <c r="AE174" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF174" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG174" t="n">
         <v>0</v>
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36109,10 +36109,10 @@
         <v>0</v>
       </c>
       <c r="AE181" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF181" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG181" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF183" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36700,10 +36700,10 @@
         <v>0</v>
       </c>
       <c r="AE184" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF184" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36848,7 +36848,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37045,17 +37045,17 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P186" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37094,10 +37094,10 @@
         <v>0</v>
       </c>
       <c r="AE186" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF186" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG186" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37242,7 +37242,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37784,7 +37784,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37972,7 +37972,7 @@
         <v>0</v>
       </c>
       <c r="BI190" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.89583333334</v>
       </c>
     </row>
     <row r="191">
@@ -37981,27 +37981,27 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q191" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38079,10 +38079,10 @@
         <v>0</v>
       </c>
       <c r="AE191" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF191" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG191" t="n">
         <v>0</v>
@@ -38169,7 +38169,7 @@
         <v>0</v>
       </c>
       <c r="BI191" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.91666666666</v>
       </c>
     </row>
     <row r="192">
@@ -38178,27 +38178,27 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38366,1188 +38366,6 @@
         <v>0</v>
       </c>
       <c r="BI192" s="3" t="n">
-        <v>46115.875</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Greece Super League</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>PAOK</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>Panathinaikos</t>
-        </is>
-      </c>
-      <c r="G193" t="n">
-        <v>0</v>
-      </c>
-      <c r="H193" t="n">
-        <v>0</v>
-      </c>
-      <c r="I193" t="n">
-        <v>0</v>
-      </c>
-      <c r="J193" t="n">
-        <v>0</v>
-      </c>
-      <c r="K193" t="n">
-        <v>0</v>
-      </c>
-      <c r="L193" t="n">
-        <v>0</v>
-      </c>
-      <c r="M193" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N193" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O193" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P193" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q193" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R193" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="S193" t="n">
-        <v>0</v>
-      </c>
-      <c r="T193" t="n">
-        <v>0</v>
-      </c>
-      <c r="U193" t="n">
-        <v>0</v>
-      </c>
-      <c r="V193" t="n">
-        <v>0</v>
-      </c>
-      <c r="W193" t="n">
-        <v>0</v>
-      </c>
-      <c r="X193" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y193" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE193" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF193" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ193" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA193" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB193" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC193" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD193" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE193" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF193" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG193" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH193" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI193" s="3" t="n">
-        <v>46115.875</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Greece Super League</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Volos NFC</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>OFI</t>
-        </is>
-      </c>
-      <c r="G194" t="n">
-        <v>0</v>
-      </c>
-      <c r="H194" t="n">
-        <v>0</v>
-      </c>
-      <c r="I194" t="n">
-        <v>0</v>
-      </c>
-      <c r="J194" t="n">
-        <v>0</v>
-      </c>
-      <c r="K194" t="n">
-        <v>0</v>
-      </c>
-      <c r="L194" t="n">
-        <v>0</v>
-      </c>
-      <c r="M194" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N194" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O194" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P194" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Q194" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="R194" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="S194" t="n">
-        <v>0</v>
-      </c>
-      <c r="T194" t="n">
-        <v>0</v>
-      </c>
-      <c r="U194" t="n">
-        <v>0</v>
-      </c>
-      <c r="V194" t="n">
-        <v>0</v>
-      </c>
-      <c r="W194" t="n">
-        <v>0</v>
-      </c>
-      <c r="X194" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y194" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE194" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF194" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ194" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA194" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB194" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC194" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD194" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE194" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF194" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG194" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH194" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI194" s="3" t="n">
-        <v>46115.875</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Italy Serie C Group B</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Sassari Torres</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>Rimini</t>
-        </is>
-      </c>
-      <c r="G195" t="n">
-        <v>0</v>
-      </c>
-      <c r="H195" t="n">
-        <v>0</v>
-      </c>
-      <c r="I195" t="n">
-        <v>0</v>
-      </c>
-      <c r="J195" t="n">
-        <v>0</v>
-      </c>
-      <c r="K195" t="n">
-        <v>0</v>
-      </c>
-      <c r="L195" t="n">
-        <v>0</v>
-      </c>
-      <c r="M195" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N195" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O195" t="inlineStr">
-        <is>
-          <t>canceled</t>
-        </is>
-      </c>
-      <c r="P195" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
-      <c r="R195" t="n">
-        <v>0</v>
-      </c>
-      <c r="S195" t="n">
-        <v>0</v>
-      </c>
-      <c r="T195" t="n">
-        <v>0</v>
-      </c>
-      <c r="U195" t="n">
-        <v>0</v>
-      </c>
-      <c r="V195" t="n">
-        <v>0</v>
-      </c>
-      <c r="W195" t="n">
-        <v>0</v>
-      </c>
-      <c r="X195" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y195" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ195" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA195" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB195" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC195" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD195" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE195" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF195" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG195" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH195" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI195" s="3" t="n">
-        <v>46115.875</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Houston Dash</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="G196" t="n">
-        <v>0</v>
-      </c>
-      <c r="H196" t="n">
-        <v>0</v>
-      </c>
-      <c r="I196" t="n">
-        <v>0</v>
-      </c>
-      <c r="J196" t="n">
-        <v>0</v>
-      </c>
-      <c r="K196" t="n">
-        <v>0</v>
-      </c>
-      <c r="L196" t="n">
-        <v>0</v>
-      </c>
-      <c r="M196" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N196" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P196" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
-      <c r="R196" t="n">
-        <v>0</v>
-      </c>
-      <c r="S196" t="n">
-        <v>0</v>
-      </c>
-      <c r="T196" t="n">
-        <v>0</v>
-      </c>
-      <c r="U196" t="n">
-        <v>0</v>
-      </c>
-      <c r="V196" t="n">
-        <v>0</v>
-      </c>
-      <c r="W196" t="n">
-        <v>0</v>
-      </c>
-      <c r="X196" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y196" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ196" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA196" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB196" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC196" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD196" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE196" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF196" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG196" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH196" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI196" s="3" t="n">
-        <v>46115.89583333334</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>Chicago Red Stars</t>
-        </is>
-      </c>
-      <c r="G197" t="n">
-        <v>0</v>
-      </c>
-      <c r="H197" t="n">
-        <v>0</v>
-      </c>
-      <c r="I197" t="n">
-        <v>0</v>
-      </c>
-      <c r="J197" t="n">
-        <v>0</v>
-      </c>
-      <c r="K197" t="n">
-        <v>0</v>
-      </c>
-      <c r="L197" t="n">
-        <v>0</v>
-      </c>
-      <c r="M197" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N197" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P197" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
-      <c r="R197" t="n">
-        <v>0</v>
-      </c>
-      <c r="S197" t="n">
-        <v>0</v>
-      </c>
-      <c r="T197" t="n">
-        <v>0</v>
-      </c>
-      <c r="U197" t="n">
-        <v>0</v>
-      </c>
-      <c r="V197" t="n">
-        <v>0</v>
-      </c>
-      <c r="W197" t="n">
-        <v>0</v>
-      </c>
-      <c r="X197" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y197" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI197" s="3" t="n">
-        <v>46115.91666666666</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Gimnasia Jujuy</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Patronato</t>
-        </is>
-      </c>
-      <c r="G198" t="n">
-        <v>0</v>
-      </c>
-      <c r="H198" t="n">
-        <v>0</v>
-      </c>
-      <c r="I198" t="n">
-        <v>0</v>
-      </c>
-      <c r="J198" t="n">
-        <v>0</v>
-      </c>
-      <c r="K198" t="n">
-        <v>0</v>
-      </c>
-      <c r="L198" t="n">
-        <v>0</v>
-      </c>
-      <c r="M198" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N198" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P198" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
-      <c r="R198" t="n">
-        <v>0</v>
-      </c>
-      <c r="S198" t="n">
-        <v>0</v>
-      </c>
-      <c r="T198" t="n">
-        <v>0</v>
-      </c>
-      <c r="U198" t="n">
-        <v>0</v>
-      </c>
-      <c r="V198" t="n">
-        <v>0</v>
-      </c>
-      <c r="W198" t="n">
-        <v>0</v>
-      </c>
-      <c r="X198" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y198" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ198" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA198" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB198" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC198" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD198" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE198" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF198" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG198" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH198" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI198" s="3" t="n">
         <v>46115.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.17</v>
+        <v>8.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.61</v>
+        <v>5.05</v>
       </c>
       <c r="R14" t="n">
-        <v>2.84</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>8.75</v>
+        <v>1.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.05</v>
+        <v>4.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>7.28</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="R16" t="n">
-        <v>7.28</v>
+        <v>4.75</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.88</v>
+        <v>3.61</v>
       </c>
       <c r="R17" t="n">
-        <v>4.75</v>
+        <v>2.84</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>7.55</v>
+        <v>2.68</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.65</v>
+        <v>3.18</v>
       </c>
       <c r="R41" t="n">
-        <v>1.33</v>
+        <v>2.6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.64</v>
+        <v>1.44</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.22</v>
+        <v>4.3</v>
       </c>
       <c r="R45" t="n">
-        <v>2.61</v>
+        <v>6.32</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.12</v>
+        <v>1.85</v>
       </c>
       <c r="Q46" t="n">
-        <v>7.5</v>
+        <v>3.64</v>
       </c>
       <c r="R46" t="n">
-        <v>19</v>
+        <v>3.96</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.72</v>
+        <v>1.31</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.54</v>
+        <v>5.05</v>
       </c>
       <c r="R48" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.43</v>
+        <v>1.79</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="R50" t="n">
-        <v>2.63</v>
+        <v>4.27</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.31</v>
+        <v>2.09</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.05</v>
+        <v>3.3</v>
       </c>
       <c r="R53" t="n">
-        <v>9.4</v>
+        <v>3.2</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.64</v>
+        <v>4.2</v>
       </c>
       <c r="R55" t="n">
-        <v>3.96</v>
+        <v>6.35</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.76</v>
+        <v>7.55</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.54</v>
+        <v>4.65</v>
       </c>
       <c r="R62" t="n">
-        <v>4.61</v>
+        <v>1.33</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.25</v>
+        <v>3.35</v>
       </c>
       <c r="R63" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>9.07</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>9.07</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,139 +17546,139 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W87" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG87" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AH87" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI87" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK87" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL87" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM87" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN87" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO87" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP87" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR87" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AS87" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AU87" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AV87" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW87" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX87" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AY87" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ87" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BA87" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BB87" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC87" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD87" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE87" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF87" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG87" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BH87" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BI87" s="3" t="n">
         <v>46115.55208333334</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,139 +17743,139 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI88" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ88" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL88" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO88" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AS88" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AT88" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AU88" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AV88" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AW88" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AY88" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AZ88" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BA88" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BB88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC88" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD88" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE88" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF88" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG88" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BH88" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BI88" s="3" t="n">
         <v>46115.55208333334</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R112" t="n">
-        <v>2.09</v>
+        <v>2.28</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,17 +23058,17 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1.9</v>
+        <v>2.47</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.54</v>
+        <v>3.18</v>
       </c>
       <c r="R118" t="n">
-        <v>3.87</v>
+        <v>2.84</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AF118" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.36</v>
+        <v>3.13</v>
       </c>
       <c r="Q119" t="n">
-        <v>4.65</v>
+        <v>3</v>
       </c>
       <c r="R119" t="n">
-        <v>6.69</v>
+        <v>2.37</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>3.16</v>
+        <v>1.99</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="R120" t="n">
-        <v>2</v>
+        <v>3.44</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF125" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.72</v>
+        <v>3.16</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="R133" t="n">
-        <v>4.65</v>
+        <v>2</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF133" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF134" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF136" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>1.88</v>
+        <v>3</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="R147" t="n">
-        <v>4.04</v>
+        <v>2.3</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF148" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF149" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="R152" t="n">
-        <v>2.89</v>
+        <v>2.58</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AF152" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>2.28</v>
+        <v>1.34</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.52</v>
+        <v>5.63</v>
       </c>
       <c r="R154" t="n">
-        <v>2.58</v>
+        <v>10.9</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,16 +30790,16 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AF154" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AG154" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH154" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI154" t="n">
         <v>0</v>
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.91</v>
+        <v>2.2</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R156" t="n">
-        <v>2.26</v>
+        <v>2.89</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,10 +31184,10 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF156" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG156" t="n">
         <v>0</v>
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.34</v>
+        <v>2.91</v>
       </c>
       <c r="Q157" t="n">
-        <v>5.63</v>
+        <v>3.2</v>
       </c>
       <c r="R157" t="n">
-        <v>10.9</v>
+        <v>2.26</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,16 +31381,16 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF157" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -32859,27 +32859,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33047,7 +33047,7 @@
         <v>0</v>
       </c>
       <c r="BI165" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.83333333334</v>
       </c>
     </row>
     <row r="166">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33154,10 +33154,10 @@
         <v>0</v>
       </c>
       <c r="AE166" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF166" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34139,10 +34139,10 @@
         <v>0</v>
       </c>
       <c r="AE171" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF171" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34730,10 +34730,10 @@
         <v>0</v>
       </c>
       <c r="AE174" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF174" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG174" t="n">
         <v>0</v>
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35666,7 +35666,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36109,10 +36109,10 @@
         <v>0</v>
       </c>
       <c r="AE181" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF181" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG181" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36257,17 +36257,17 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P182" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36700,10 +36700,10 @@
         <v>0</v>
       </c>
       <c r="AE184" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF184" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36848,7 +36848,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37045,7 +37045,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37291,10 +37291,10 @@
         <v>0</v>
       </c>
       <c r="AE187" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF187" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG187" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G189" t="n">

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI192"/>
+  <dimension ref="A1:BI188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>8.75</v>
+        <v>2.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.05</v>
+        <v>3.61</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>2.84</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.36</v>
+        <v>8.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.4</v>
+        <v>5.05</v>
       </c>
       <c r="R15" t="n">
-        <v>7.28</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="R16" t="n">
-        <v>4.75</v>
+        <v>7.28</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.61</v>
+        <v>3.88</v>
       </c>
       <c r="R17" t="n">
-        <v>2.84</v>
+        <v>4.75</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.54</v>
+        <v>4.15</v>
       </c>
       <c r="R30" t="n">
-        <v>4.9</v>
+        <v>5.32</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="R31" t="n">
-        <v>4.61</v>
+        <v>3.25</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="R34" t="n">
-        <v>2.99</v>
+        <v>6.35</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="R36" t="n">
-        <v>2.34</v>
+        <v>6.32</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R40" t="n">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.68</v>
+        <v>2.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="R41" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.12</v>
+        <v>2.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>7.5</v>
+        <v>3.25</v>
       </c>
       <c r="R42" t="n">
-        <v>19</v>
+        <v>2.95</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.44</v>
+        <v>7.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="R45" t="n">
-        <v>6.32</v>
+        <v>1.33</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.85</v>
+        <v>1.31</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.64</v>
+        <v>5.05</v>
       </c>
       <c r="R46" t="n">
-        <v>3.96</v>
+        <v>9.4</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.64</v>
+        <v>2.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="R49" t="n">
-        <v>4.5</v>
+        <v>2.96</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,55 +10257,55 @@
         </is>
       </c>
       <c r="P50" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="R50" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF50" t="n">
         <v>1.79</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R50" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1.88</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R51" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="R52" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R55" t="n">
-        <v>6.35</v>
+        <v>6.4</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.15</v>
+        <v>1.85</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.08</v>
+        <v>3.64</v>
       </c>
       <c r="R60" t="n">
-        <v>2.35</v>
+        <v>3.96</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>7.55</v>
+        <v>1.72</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.65</v>
+        <v>3.54</v>
       </c>
       <c r="R62" t="n">
-        <v>1.33</v>
+        <v>4.9</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="R63" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12962,12 +12962,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>46115.47916666666</v>
+        <v>46115.45833333334</v>
       </c>
     </row>
     <row r="65">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46115.5</v>
+        <v>46115.47916666666</v>
       </c>
     </row>
     <row r="68">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14341,27 +14341,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46115.51041666666</v>
+        <v>46115.5</v>
       </c>
     </row>
     <row r="72">
@@ -14538,27 +14538,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14726,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>46115.52083333334</v>
+        <v>46115.51041666666</v>
       </c>
     </row>
     <row r="73">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="R73" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15129,12 +15129,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46115.54166666666</v>
+        <v>46115.52083333334</v>
       </c>
     </row>
     <row r="76">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.87</v>
+        <v>4.19</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="R80" t="n">
-        <v>3.91</v>
+        <v>1.77</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF80" t="n">
         <v>1.85</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.02</v>
+        <v>3.8</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R83" t="n">
-        <v>3.31</v>
+        <v>1.85</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>4.19</v>
+        <v>1.79</v>
       </c>
       <c r="Q86" t="n">
         <v>3.7</v>
       </c>
       <c r="R86" t="n">
-        <v>1.77</v>
+        <v>4.09</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17397,7 +17397,7 @@
         <v>1.83</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17493,27 +17493,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,142 +17546,142 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI87" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ87" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK87" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL87" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM87" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN87" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO87" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AR87" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AS87" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AT87" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AU87" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AV87" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AW87" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX87" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AY87" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AZ87" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BA87" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BB87" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC87" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD87" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE87" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF87" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG87" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BH87" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>46115.55208333334</v>
+        <v>46115.54166666666</v>
       </c>
     </row>
     <row r="88">
@@ -17690,12 +17690,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
         <v>0</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>46115.55208333334</v>
+        <v>46115.54166666666</v>
       </c>
     </row>
     <row r="89">
@@ -17887,12 +17887,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18075,7 +18075,7 @@
         <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>46115.5625</v>
+        <v>46115.55208333334</v>
       </c>
     </row>
     <row r="90">
@@ -18084,12 +18084,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,142 +18137,142 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V90" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI90" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL90" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM90" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN90" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO90" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP90" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR90" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AS90" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AT90" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AU90" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AV90" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW90" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX90" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AY90" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ90" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BA90" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BB90" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC90" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD90" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE90" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF90" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG90" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BH90" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>46115.57291666666</v>
+        <v>46115.55208333334</v>
       </c>
     </row>
     <row r="91">
@@ -18281,12 +18281,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46115.57291666666</v>
+        <v>46115.5625</v>
       </c>
     </row>
     <row r="92">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18675,12 +18675,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>46115.58333333334</v>
+        <v>46115.57291666666</v>
       </c>
     </row>
     <row r="94">
@@ -18872,12 +18872,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46115.58333333334</v>
+        <v>46115.57291666666</v>
       </c>
     </row>
     <row r="95">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20842,12 +20842,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.52</v>
+        <v>3.68</v>
       </c>
       <c r="R104" t="n">
-        <v>3.36</v>
+        <v>5</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21030,7 +21030,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3" t="n">
-        <v>46115.60416666666</v>
+        <v>46115.58333333334</v>
       </c>
     </row>
     <row r="105">
@@ -21039,12 +21039,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21227,7 +21227,7 @@
         <v>0</v>
       </c>
       <c r="BI105" s="3" t="n">
-        <v>46115.60416666666</v>
+        <v>46115.58333333334</v>
       </c>
     </row>
     <row r="106">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.65</v>
+        <v>2.26</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R106" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="Q108" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="R108" t="n">
-        <v>4.95</v>
+        <v>4.25</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="Q109" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="R109" t="n">
-        <v>6.05</v>
+        <v>4.95</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="R110" t="n">
-        <v>4.25</v>
+        <v>6.05</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.39</v>
+        <v>3.56</v>
       </c>
       <c r="Q113" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="R113" t="n">
-        <v>3.16</v>
+        <v>2.09</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R114" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,17 +23058,17 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="Q116" t="n">
         <v>3.2</v>
       </c>
       <c r="R116" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R117" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23600,12 +23600,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.47</v>
+        <v>1.93</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.18</v>
+        <v>3.52</v>
       </c>
       <c r="R118" t="n">
-        <v>2.84</v>
+        <v>3.36</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF118" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23788,7 +23788,7 @@
         <v>0</v>
       </c>
       <c r="BI118" s="3" t="n">
-        <v>46115.625</v>
+        <v>46115.60416666666</v>
       </c>
     </row>
     <row r="119">
@@ -23797,12 +23797,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>3.13</v>
+        <v>2.39</v>
       </c>
       <c r="Q119" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R119" t="n">
-        <v>2.37</v>
+        <v>3.16</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="BI119" s="3" t="n">
-        <v>46115.625</v>
+        <v>46115.60416666666</v>
       </c>
     </row>
     <row r="120">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.54</v>
+        <v>4.65</v>
       </c>
       <c r="R124" t="n">
-        <v>3.87</v>
+        <v>6.69</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R125" t="n">
-        <v>4.65</v>
+        <v>3.44</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AF125" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF127" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26259,10 +26259,10 @@
         <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF131" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>6.69</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>3.16</v>
+        <v>1.9</v>
       </c>
       <c r="Q133" t="n">
         <v>3.54</v>
       </c>
       <c r="R133" t="n">
-        <v>2</v>
+        <v>3.87</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF133" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27343,12 +27343,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27531,7 +27531,7 @@
         <v>0</v>
       </c>
       <c r="BI137" s="3" t="n">
-        <v>46115.63541666666</v>
+        <v>46115.625</v>
       </c>
     </row>
     <row r="138">
@@ -27540,12 +27540,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27728,7 +27728,7 @@
         <v>0</v>
       </c>
       <c r="BI138" s="3" t="n">
-        <v>46115.63541666666</v>
+        <v>46115.625</v>
       </c>
     </row>
     <row r="139">
@@ -27737,12 +27737,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27925,7 +27925,7 @@
         <v>0</v>
       </c>
       <c r="BI139" s="3" t="n">
-        <v>46115.64583333334</v>
+        <v>46115.63541666666</v>
       </c>
     </row>
     <row r="140">
@@ -27934,12 +27934,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28122,7 +28122,7 @@
         <v>0</v>
       </c>
       <c r="BI140" s="3" t="n">
-        <v>46115.64583333334</v>
+        <v>46115.63541666666</v>
       </c>
     </row>
     <row r="141">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29313,12 +29313,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29501,7 +29501,7 @@
         <v>0</v>
       </c>
       <c r="BI147" s="3" t="n">
-        <v>46115.65625</v>
+        <v>46115.64583333334</v>
       </c>
     </row>
     <row r="148">
@@ -29510,27 +29510,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF148" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29698,7 +29698,7 @@
         <v>0</v>
       </c>
       <c r="BI148" s="3" t="n">
-        <v>46115.65625</v>
+        <v>46115.64583333334</v>
       </c>
     </row>
     <row r="149">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="R152" t="n">
-        <v>2.58</v>
+        <v>4.04</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF152" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30500,22 +30500,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1.88</v>
+        <v>1.34</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.48</v>
+        <v>5.63</v>
       </c>
       <c r="R153" t="n">
-        <v>4.04</v>
+        <v>10.9</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,16 +30593,16 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF153" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG153" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH153" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI153" t="n">
         <v>0</v>
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>1.34</v>
+        <v>5.35</v>
       </c>
       <c r="Q154" t="n">
-        <v>5.63</v>
+        <v>4.05</v>
       </c>
       <c r="R154" t="n">
-        <v>10.9</v>
+        <v>1.58</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,16 +30790,16 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AF154" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="AG154" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH154" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI154" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1.39</v>
+        <v>2.28</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.75</v>
+        <v>3.52</v>
       </c>
       <c r="R155" t="n">
-        <v>7.28</v>
+        <v>2.58</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30987,10 +30987,10 @@
         <v>0</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AF155" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AG155" t="n">
         <v>0</v>
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.2</v>
+        <v>2.91</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R156" t="n">
-        <v>2.89</v>
+        <v>2.26</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,10 +31184,10 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF156" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.91</v>
+        <v>3.99</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="R157" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31480,27 +31480,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF158" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG158" t="n">
         <v>0</v>
@@ -31668,7 +31668,7 @@
         <v>0</v>
       </c>
       <c r="BI158" s="3" t="n">
-        <v>46115.66666666666</v>
+        <v>46115.65625</v>
       </c>
     </row>
     <row r="159">
@@ -31677,7 +31677,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>3.29</v>
+        <v>1.39</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.28</v>
+        <v>4.75</v>
       </c>
       <c r="R159" t="n">
-        <v>2.18</v>
+        <v>7.28</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31775,10 +31775,10 @@
         <v>0</v>
       </c>
       <c r="AE159" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF159" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG159" t="n">
         <v>0</v>
@@ -31865,7 +31865,7 @@
         <v>0</v>
       </c>
       <c r="BI159" s="3" t="n">
-        <v>46115.66666666666</v>
+        <v>46115.65625</v>
       </c>
     </row>
     <row r="160">
@@ -32071,12 +32071,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF161" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32259,7 +32259,7 @@
         <v>0</v>
       </c>
       <c r="BI161" s="3" t="n">
-        <v>46115.6875</v>
+        <v>46115.66666666666</v>
       </c>
     </row>
     <row r="162">
@@ -32268,12 +32268,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>1.45</v>
+        <v>3.29</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="R162" t="n">
-        <v>7.15</v>
+        <v>2.18</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF162" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -32456,7 +32456,7 @@
         <v>0</v>
       </c>
       <c r="BI162" s="3" t="n">
-        <v>46115.72916666666</v>
+        <v>46115.66666666666</v>
       </c>
     </row>
     <row r="163">
@@ -32465,27 +32465,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32563,10 +32563,10 @@
         <v>0</v>
       </c>
       <c r="AE163" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF163" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG163" t="n">
         <v>0</v>
@@ -32653,7 +32653,7 @@
         <v>0</v>
       </c>
       <c r="BI163" s="3" t="n">
-        <v>46115.83333333334</v>
+        <v>46115.6875</v>
       </c>
     </row>
     <row r="164">
@@ -32662,7 +32662,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32715,13 +32715,13 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q164" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R164" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -32760,10 +32760,10 @@
         <v>0</v>
       </c>
       <c r="AE164" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF164" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG164" t="n">
         <v>0</v>
@@ -32850,7 +32850,7 @@
         <v>0</v>
       </c>
       <c r="BI164" s="3" t="n">
-        <v>46115.83333333334</v>
+        <v>46115.72916666666</v>
       </c>
     </row>
     <row r="165">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33056,27 +33056,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33154,10 +33154,10 @@
         <v>0</v>
       </c>
       <c r="AE166" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF166" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG166" t="n">
         <v>0</v>
@@ -33244,7 +33244,7 @@
         <v>0</v>
       </c>
       <c r="BI166" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.83333333334</v>
       </c>
     </row>
     <row r="167">
@@ -33253,27 +33253,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33441,7 +33441,7 @@
         <v>0</v>
       </c>
       <c r="BI167" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.83333333334</v>
       </c>
     </row>
     <row r="168">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33696,7 +33696,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q170" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -33942,10 +33942,10 @@
         <v>0</v>
       </c>
       <c r="AE170" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF170" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG170" t="n">
         <v>0</v>
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34139,10 +34139,10 @@
         <v>0</v>
       </c>
       <c r="AE171" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF171" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34730,10 +34730,10 @@
         <v>0</v>
       </c>
       <c r="AE174" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF174" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q176" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35124,10 +35124,10 @@
         <v>0</v>
       </c>
       <c r="AE176" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF176" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG176" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35518,10 +35518,10 @@
         <v>0</v>
       </c>
       <c r="AE178" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF178" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG178" t="n">
         <v>0</v>
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35666,7 +35666,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,22 +36016,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF183" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36996,27 +36996,27 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37184,7 +37184,7 @@
         <v>0</v>
       </c>
       <c r="BI186" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.89583333334</v>
       </c>
     </row>
     <row r="187">
@@ -37193,27 +37193,27 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37291,10 +37291,10 @@
         <v>0</v>
       </c>
       <c r="AE187" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF187" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG187" t="n">
         <v>0</v>
@@ -37381,7 +37381,7 @@
         <v>0</v>
       </c>
       <c r="BI187" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.91666666666</v>
       </c>
     </row>
     <row r="188">
@@ -37390,27 +37390,27 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37578,794 +37578,6 @@
         <v>0</v>
       </c>
       <c r="BI188" s="3" t="n">
-        <v>46115.875</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Železničar Pančevo</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Novi Pazar</t>
-        </is>
-      </c>
-      <c r="G189" t="n">
-        <v>0</v>
-      </c>
-      <c r="H189" t="n">
-        <v>0</v>
-      </c>
-      <c r="I189" t="n">
-        <v>0</v>
-      </c>
-      <c r="J189" t="n">
-        <v>0</v>
-      </c>
-      <c r="K189" t="n">
-        <v>0</v>
-      </c>
-      <c r="L189" t="n">
-        <v>0</v>
-      </c>
-      <c r="M189" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N189" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O189" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P189" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
-      <c r="R189" t="n">
-        <v>0</v>
-      </c>
-      <c r="S189" t="n">
-        <v>0</v>
-      </c>
-      <c r="T189" t="n">
-        <v>0</v>
-      </c>
-      <c r="U189" t="n">
-        <v>0</v>
-      </c>
-      <c r="V189" t="n">
-        <v>0</v>
-      </c>
-      <c r="W189" t="n">
-        <v>0</v>
-      </c>
-      <c r="X189" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y189" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ189" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA189" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB189" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC189" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD189" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE189" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF189" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG189" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH189" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI189" s="3" t="n">
-        <v>46115.875</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Houston Dash</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="G190" t="n">
-        <v>0</v>
-      </c>
-      <c r="H190" t="n">
-        <v>0</v>
-      </c>
-      <c r="I190" t="n">
-        <v>0</v>
-      </c>
-      <c r="J190" t="n">
-        <v>0</v>
-      </c>
-      <c r="K190" t="n">
-        <v>0</v>
-      </c>
-      <c r="L190" t="n">
-        <v>0</v>
-      </c>
-      <c r="M190" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N190" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O190" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P190" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
-      <c r="R190" t="n">
-        <v>0</v>
-      </c>
-      <c r="S190" t="n">
-        <v>0</v>
-      </c>
-      <c r="T190" t="n">
-        <v>0</v>
-      </c>
-      <c r="U190" t="n">
-        <v>0</v>
-      </c>
-      <c r="V190" t="n">
-        <v>0</v>
-      </c>
-      <c r="W190" t="n">
-        <v>0</v>
-      </c>
-      <c r="X190" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y190" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ190" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA190" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB190" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC190" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD190" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE190" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF190" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG190" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH190" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI190" s="3" t="n">
-        <v>46115.89583333334</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>Chicago Red Stars</t>
-        </is>
-      </c>
-      <c r="G191" t="n">
-        <v>0</v>
-      </c>
-      <c r="H191" t="n">
-        <v>0</v>
-      </c>
-      <c r="I191" t="n">
-        <v>0</v>
-      </c>
-      <c r="J191" t="n">
-        <v>0</v>
-      </c>
-      <c r="K191" t="n">
-        <v>0</v>
-      </c>
-      <c r="L191" t="n">
-        <v>0</v>
-      </c>
-      <c r="M191" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N191" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O191" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P191" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
-      <c r="R191" t="n">
-        <v>0</v>
-      </c>
-      <c r="S191" t="n">
-        <v>0</v>
-      </c>
-      <c r="T191" t="n">
-        <v>0</v>
-      </c>
-      <c r="U191" t="n">
-        <v>0</v>
-      </c>
-      <c r="V191" t="n">
-        <v>0</v>
-      </c>
-      <c r="W191" t="n">
-        <v>0</v>
-      </c>
-      <c r="X191" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y191" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ191" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA191" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB191" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC191" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD191" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE191" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF191" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG191" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH191" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI191" s="3" t="n">
-        <v>46115.91666666666</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Gimnasia Jujuy</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>Patronato</t>
-        </is>
-      </c>
-      <c r="G192" t="n">
-        <v>0</v>
-      </c>
-      <c r="H192" t="n">
-        <v>0</v>
-      </c>
-      <c r="I192" t="n">
-        <v>0</v>
-      </c>
-      <c r="J192" t="n">
-        <v>0</v>
-      </c>
-      <c r="K192" t="n">
-        <v>0</v>
-      </c>
-      <c r="L192" t="n">
-        <v>0</v>
-      </c>
-      <c r="M192" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N192" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O192" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P192" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
-      <c r="R192" t="n">
-        <v>0</v>
-      </c>
-      <c r="S192" t="n">
-        <v>0</v>
-      </c>
-      <c r="T192" t="n">
-        <v>0</v>
-      </c>
-      <c r="U192" t="n">
-        <v>0</v>
-      </c>
-      <c r="V192" t="n">
-        <v>0</v>
-      </c>
-      <c r="W192" t="n">
-        <v>0</v>
-      </c>
-      <c r="X192" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y192" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ192" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA192" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB192" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC192" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD192" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE192" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF192" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG192" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH192" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI192" s="3" t="n">
         <v>46115.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.61</v>
+        <v>3.88</v>
       </c>
       <c r="R14" t="n">
-        <v>2.84</v>
+        <v>4.75</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>8.75</v>
+        <v>2.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.05</v>
+        <v>3.61</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>2.84</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.67</v>
+        <v>8.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.88</v>
+        <v>5.05</v>
       </c>
       <c r="R17" t="n">
-        <v>4.75</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="R30" t="n">
-        <v>5.32</v>
+        <v>6.4</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.06</v>
+        <v>2.43</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="R31" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.79</v>
+        <v>2.09</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>4.27</v>
+        <v>3.2</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.3</v>
+        <v>7.5</v>
       </c>
       <c r="R36" t="n">
-        <v>6.32</v>
+        <v>19</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="R40" t="n">
-        <v>2.34</v>
+        <v>6.32</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>7.55</v>
+        <v>2.29</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.65</v>
+        <v>3.15</v>
       </c>
       <c r="R45" t="n">
-        <v>1.33</v>
+        <v>2.99</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.31</v>
+        <v>2.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.05</v>
+        <v>3.25</v>
       </c>
       <c r="R46" t="n">
-        <v>9.4</v>
+        <v>2.34</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.4</v>
+        <v>1.64</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="R49" t="n">
-        <v>2.96</v>
+        <v>4.5</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.54</v>
+        <v>3.15</v>
       </c>
       <c r="R50" t="n">
-        <v>4.61</v>
+        <v>3.25</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R51" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.64</v>
+        <v>2.68</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.25</v>
+        <v>3.18</v>
       </c>
       <c r="R52" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.33</v>
+        <v>3.65</v>
       </c>
       <c r="R55" t="n">
-        <v>6.4</v>
+        <v>4.27</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.68</v>
+        <v>1.85</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.22</v>
+        <v>3.64</v>
       </c>
       <c r="R57" t="n">
-        <v>2.57</v>
+        <v>3.96</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.08</v>
+        <v>3.54</v>
       </c>
       <c r="R59" t="n">
-        <v>2.35</v>
+        <v>4.9</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="R60" t="n">
-        <v>3.96</v>
+        <v>2.96</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.12</v>
+        <v>7.55</v>
       </c>
       <c r="Q61" t="n">
-        <v>7.5</v>
+        <v>4.65</v>
       </c>
       <c r="R61" t="n">
-        <v>19</v>
+        <v>1.33</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.72</v>
+        <v>2.64</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.54</v>
+        <v>3.22</v>
       </c>
       <c r="R62" t="n">
-        <v>4.9</v>
+        <v>2.61</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12669,7 +12669,7 @@
         <v>1.98</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.43</v>
+        <v>2.68</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.58</v>
+        <v>3.22</v>
       </c>
       <c r="R63" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.64</v>
+        <v>1.76</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.22</v>
+        <v>3.54</v>
       </c>
       <c r="R64" t="n">
-        <v>2.61</v>
+        <v>4.61</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13063,7 +13063,7 @@
         <v>1.98</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>9.07</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>9.07</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,55 +15379,55 @@
         </is>
       </c>
       <c r="P76" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R76" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF76" t="n">
         <v>1.87</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R76" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" t="n">
-        <v>0</v>
-      </c>
-      <c r="W76" t="n">
-        <v>0</v>
-      </c>
-      <c r="X76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>1.85</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R83" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.79</v>
+        <v>3.8</v>
       </c>
       <c r="Q86" t="n">
         <v>3.7</v>
       </c>
       <c r="R86" t="n">
-        <v>4.09</v>
+        <v>1.85</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.5</v>
+        <v>4.19</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="R88" t="n">
-        <v>2.7</v>
+        <v>1.77</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17791,7 +17791,7 @@
         <v>1.83</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.26</v>
+        <v>1.78</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R106" t="n">
-        <v>2.89</v>
+        <v>4.25</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>3.85</v>
+        <v>2.39</v>
       </c>
       <c r="Q107" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R107" t="n">
-        <v>2.02</v>
+        <v>3.16</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="Q108" t="n">
         <v>3.4</v>
       </c>
       <c r="R108" t="n">
-        <v>4.25</v>
+        <v>2.6</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1.59</v>
+        <v>2.06</v>
       </c>
       <c r="Q109" t="n">
-        <v>4.1</v>
+        <v>3.24</v>
       </c>
       <c r="R109" t="n">
-        <v>4.95</v>
+        <v>3.65</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.49</v>
+        <v>3.75</v>
       </c>
       <c r="Q110" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R110" t="n">
-        <v>6.05</v>
+        <v>1.96</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.06</v>
+        <v>1.59</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.24</v>
+        <v>4.1</v>
       </c>
       <c r="R111" t="n">
-        <v>3.65</v>
+        <v>4.95</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>3.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q112" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="R112" t="n">
-        <v>2.28</v>
+        <v>2.89</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>3.56</v>
+        <v>3.85</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R113" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R114" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="Q116" t="n">
         <v>3.2</v>
       </c>
       <c r="R116" t="n">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1.93</v>
+        <v>1.49</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="R118" t="n">
-        <v>3.36</v>
+        <v>6.05</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="Q119" t="n">
-        <v>2.8</v>
+        <v>3.52</v>
       </c>
       <c r="R119" t="n">
-        <v>3.16</v>
+        <v>3.36</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="Q124" t="n">
-        <v>4.65</v>
+        <v>3.54</v>
       </c>
       <c r="R124" t="n">
-        <v>6.69</v>
+        <v>3.87</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF127" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>3.16</v>
+        <v>1.99</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="R129" t="n">
-        <v>2</v>
+        <v>3.44</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF130" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26259,10 +26259,10 @@
         <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF131" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF133" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R139" t="n">
-        <v>3.7</v>
+        <v>1.85</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q140" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R140" t="n">
         <v>3.7</v>
-      </c>
-      <c r="R140" t="n">
-        <v>1.85</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>3</v>
+        <v>1.39</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="R149" t="n">
-        <v>2.3</v>
+        <v>7.28</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF149" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF150" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1.88</v>
+        <v>6.12</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.48</v>
+        <v>3.98</v>
       </c>
       <c r="R152" t="n">
-        <v>4.04</v>
+        <v>1.46</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF152" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30500,22 +30500,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1.34</v>
+        <v>3.99</v>
       </c>
       <c r="Q153" t="n">
-        <v>5.63</v>
+        <v>3.38</v>
       </c>
       <c r="R153" t="n">
-        <v>10.9</v>
+        <v>1.92</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,16 +30593,16 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF153" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG153" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH153" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI153" t="n">
         <v>0</v>
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>5.35</v>
+        <v>3</v>
       </c>
       <c r="Q154" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="R154" t="n">
-        <v>1.58</v>
+        <v>2.3</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,10 +30790,10 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF154" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG154" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>3.99</v>
+        <v>2.01</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="R157" t="n">
-        <v>1.92</v>
+        <v>3.47</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>2.2</v>
+        <v>1.34</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.35</v>
+        <v>5.63</v>
       </c>
       <c r="R158" t="n">
-        <v>2.89</v>
+        <v>10.9</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,16 +31578,16 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AF158" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AG158" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH158" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI158" t="n">
         <v>0</v>
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>1.39</v>
+        <v>5.35</v>
       </c>
       <c r="Q159" t="n">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="R159" t="n">
-        <v>7.28</v>
+        <v>1.58</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31775,10 +31775,10 @@
         <v>0</v>
       </c>
       <c r="AE159" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF159" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AG159" t="n">
         <v>0</v>
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -33455,22 +33455,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q168" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33548,10 +33548,10 @@
         <v>0</v>
       </c>
       <c r="AE168" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF168" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33696,17 +33696,17 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33745,10 +33745,10 @@
         <v>0</v>
       </c>
       <c r="AE169" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF169" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33893,17 +33893,17 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P170" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -33942,10 +33942,10 @@
         <v>0</v>
       </c>
       <c r="AE170" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF170" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG170" t="n">
         <v>0</v>
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q172" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34730,10 +34730,10 @@
         <v>0</v>
       </c>
       <c r="AE174" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF174" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q176" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35124,10 +35124,10 @@
         <v>0</v>
       </c>
       <c r="AE176" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF176" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG176" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q178" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35518,10 +35518,10 @@
         <v>0</v>
       </c>
       <c r="AE178" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF178" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG178" t="n">
         <v>0</v>
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,22 +36016,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36257,7 +36257,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF183" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36651,7 +36651,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q185" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -36897,10 +36897,10 @@
         <v>0</v>
       </c>
       <c r="AE185" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF185" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG185" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G188" t="n">

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI188"/>
+  <dimension ref="A1:BI186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.88</v>
+        <v>3.61</v>
       </c>
       <c r="R14" t="n">
-        <v>4.75</v>
+        <v>2.84</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.17</v>
+        <v>8.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.61</v>
+        <v>5.05</v>
       </c>
       <c r="R15" t="n">
-        <v>2.84</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>7.28</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>8.75</v>
+        <v>1.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.05</v>
+        <v>4.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>7.28</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.47</v>
+        <v>1.12</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.33</v>
+        <v>7.5</v>
       </c>
       <c r="R30" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.43</v>
+        <v>3.15</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="R31" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.09</v>
+        <v>7.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>4.65</v>
       </c>
       <c r="R32" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.12</v>
+        <v>2.64</v>
       </c>
       <c r="Q36" t="n">
-        <v>7.5</v>
+        <v>3.22</v>
       </c>
       <c r="R36" t="n">
-        <v>19</v>
+        <v>2.61</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.44</v>
+        <v>2.68</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.2</v>
+        <v>3.18</v>
       </c>
       <c r="R39" t="n">
-        <v>6.35</v>
+        <v>2.6</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="R40" t="n">
-        <v>6.32</v>
+        <v>3.25</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="R45" t="n">
-        <v>2.99</v>
+        <v>6.32</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="R46" t="n">
-        <v>2.34</v>
+        <v>6.35</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.55</v>
+        <v>2.06</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="R48" t="n">
-        <v>5.32</v>
+        <v>3.25</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.25</v>
+        <v>3.54</v>
       </c>
       <c r="R49" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R50" t="n">
-        <v>3.25</v>
+        <v>2.34</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.35</v>
+        <v>4.15</v>
       </c>
       <c r="R51" t="n">
-        <v>3.4</v>
+        <v>5.32</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.68</v>
+        <v>2.29</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="R52" t="n">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.05</v>
+        <v>4.25</v>
       </c>
       <c r="R53" t="n">
-        <v>9.4</v>
+        <v>4.5</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.79</v>
+        <v>1.47</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="R55" t="n">
-        <v>4.27</v>
+        <v>6.4</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="R60" t="n">
-        <v>2.96</v>
+        <v>4.61</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>7.55</v>
+        <v>2.43</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.65</v>
+        <v>3.58</v>
       </c>
       <c r="R61" t="n">
-        <v>1.33</v>
+        <v>2.63</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.68</v>
+        <v>1.31</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.22</v>
+        <v>5.05</v>
       </c>
       <c r="R63" t="n">
-        <v>2.57</v>
+        <v>9.4</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.12</v>
+        <v>1.35</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.2</v>
+        <v>4.72</v>
       </c>
       <c r="R65" t="n">
-        <v>3.46</v>
+        <v>9.07</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.72</v>
+        <v>3.2</v>
       </c>
       <c r="R67" t="n">
-        <v>9.07</v>
+        <v>3.46</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.79</v>
+        <v>3.8</v>
       </c>
       <c r="Q76" t="n">
         <v>3.7</v>
       </c>
       <c r="R76" t="n">
-        <v>4.09</v>
+        <v>1.85</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R86" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.78</v>
+        <v>3.75</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R106" t="n">
-        <v>4.25</v>
+        <v>1.96</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.39</v>
+        <v>1.78</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="R107" t="n">
-        <v>3.16</v>
+        <v>4.25</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF107" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R108" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.06</v>
+        <v>2.39</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.24</v>
+        <v>2.8</v>
       </c>
       <c r="R109" t="n">
-        <v>3.65</v>
+        <v>3.16</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R110" t="n">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.59</v>
+        <v>2.26</v>
       </c>
       <c r="Q111" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="R111" t="n">
-        <v>4.95</v>
+        <v>2.89</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.26</v>
+        <v>1.49</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="R112" t="n">
-        <v>2.89</v>
+        <v>6.05</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="Q113" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R113" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22861,17 +22861,17 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,17 +23058,17 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>3.56</v>
+        <v>2.06</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="R116" t="n">
-        <v>2.09</v>
+        <v>3.65</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF116" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.65</v>
+        <v>3.85</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R117" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1.49</v>
+        <v>1.93</v>
       </c>
       <c r="Q118" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="R118" t="n">
-        <v>6.05</v>
+        <v>3.36</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.93</v>
+        <v>1.59</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="R119" t="n">
-        <v>3.36</v>
+        <v>4.95</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>1.72</v>
+        <v>3.16</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="R120" t="n">
-        <v>4.65</v>
+        <v>2</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>6.69</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF129" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF130" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF133" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>3.13</v>
+        <v>1.72</v>
       </c>
       <c r="Q134" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="R134" t="n">
-        <v>2.37</v>
+        <v>4.65</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF134" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF136" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF137" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q139" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R139" t="n">
         <v>3.7</v>
-      </c>
-      <c r="R139" t="n">
-        <v>1.85</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R140" t="n">
-        <v>3.7</v>
+        <v>1.85</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.39</v>
+        <v>1.88</v>
       </c>
       <c r="Q149" t="n">
-        <v>4.75</v>
+        <v>3.48</v>
       </c>
       <c r="R149" t="n">
-        <v>7.28</v>
+        <v>4.04</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF149" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.2</v>
+        <v>3.99</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="R150" t="n">
-        <v>2.89</v>
+        <v>1.92</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF150" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>1.88</v>
+        <v>1.34</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.48</v>
+        <v>5.63</v>
       </c>
       <c r="R151" t="n">
-        <v>4.04</v>
+        <v>10.9</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,16 +30199,16 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF151" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG151" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH151" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI151" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>6.12</v>
+        <v>3</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="R152" t="n">
-        <v>1.46</v>
+        <v>2.3</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF152" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>3.99</v>
+        <v>2.91</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="R153" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>3</v>
+        <v>5.35</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="R154" t="n">
-        <v>2.3</v>
+        <v>1.58</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,10 +30790,10 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF154" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG154" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>2.28</v>
+        <v>1.39</v>
       </c>
       <c r="Q155" t="n">
-        <v>3.52</v>
+        <v>4.75</v>
       </c>
       <c r="R155" t="n">
-        <v>2.58</v>
+        <v>7.28</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30987,10 +30987,10 @@
         <v>0</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AF155" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AG155" t="n">
         <v>0</v>
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.91</v>
+        <v>6.12</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.2</v>
+        <v>3.98</v>
       </c>
       <c r="R156" t="n">
-        <v>2.26</v>
+        <v>1.46</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,10 +31184,10 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF156" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG156" t="n">
         <v>0</v>
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>1.34</v>
+        <v>2.2</v>
       </c>
       <c r="Q158" t="n">
-        <v>5.63</v>
+        <v>3.35</v>
       </c>
       <c r="R158" t="n">
-        <v>10.9</v>
+        <v>2.89</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,16 +31578,16 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AF158" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AG158" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH158" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>5.35</v>
+        <v>2.28</v>
       </c>
       <c r="Q159" t="n">
-        <v>4.05</v>
+        <v>3.52</v>
       </c>
       <c r="R159" t="n">
-        <v>1.58</v>
+        <v>2.58</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31775,10 +31775,10 @@
         <v>0</v>
       </c>
       <c r="AE159" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF159" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AG159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF160" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>3.29</v>
+        <v>1.47</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.28</v>
+        <v>4.3</v>
       </c>
       <c r="R161" t="n">
-        <v>2.18</v>
+        <v>6.46</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF161" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -33455,22 +33455,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33548,10 +33548,10 @@
         <v>0</v>
       </c>
       <c r="AE168" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF168" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33745,10 +33745,10 @@
         <v>0</v>
       </c>
       <c r="AE169" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF169" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33893,7 +33893,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34090,7 +34090,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34730,10 +34730,10 @@
         <v>0</v>
       </c>
       <c r="AE174" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF174" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG174" t="n">
         <v>0</v>
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -34927,10 +34927,10 @@
         <v>0</v>
       </c>
       <c r="AE175" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF175" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG175" t="n">
         <v>0</v>
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35321,10 +35321,10 @@
         <v>0</v>
       </c>
       <c r="AE177" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF177" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG177" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35469,7 +35469,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q180" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36109,10 +36109,10 @@
         <v>0</v>
       </c>
       <c r="AE181" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF181" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG181" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF183" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36602,27 +36602,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36651,7 +36651,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -36790,7 +36790,7 @@
         <v>0</v>
       </c>
       <c r="BI184" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.89583333334</v>
       </c>
     </row>
     <row r="185">
@@ -36799,27 +36799,27 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q185" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -36897,10 +36897,10 @@
         <v>0</v>
       </c>
       <c r="AE185" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF185" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG185" t="n">
         <v>0</v>
@@ -36987,7 +36987,7 @@
         <v>0</v>
       </c>
       <c r="BI185" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.91666666666</v>
       </c>
     </row>
     <row r="186">
@@ -36996,7 +36996,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37184,400 +37184,6 @@
         <v>0</v>
       </c>
       <c r="BI186" s="3" t="n">
-        <v>46115.89583333334</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>Chicago Red Stars</t>
-        </is>
-      </c>
-      <c r="G187" t="n">
-        <v>0</v>
-      </c>
-      <c r="H187" t="n">
-        <v>0</v>
-      </c>
-      <c r="I187" t="n">
-        <v>0</v>
-      </c>
-      <c r="J187" t="n">
-        <v>0</v>
-      </c>
-      <c r="K187" t="n">
-        <v>0</v>
-      </c>
-      <c r="L187" t="n">
-        <v>0</v>
-      </c>
-      <c r="M187" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N187" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O187" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P187" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
-      <c r="R187" t="n">
-        <v>0</v>
-      </c>
-      <c r="S187" t="n">
-        <v>0</v>
-      </c>
-      <c r="T187" t="n">
-        <v>0</v>
-      </c>
-      <c r="U187" t="n">
-        <v>0</v>
-      </c>
-      <c r="V187" t="n">
-        <v>0</v>
-      </c>
-      <c r="W187" t="n">
-        <v>0</v>
-      </c>
-      <c r="X187" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y187" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ187" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA187" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB187" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC187" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD187" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE187" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF187" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG187" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH187" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI187" s="3" t="n">
-        <v>46115.91666666666</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Gimnasia Jujuy</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>Patronato</t>
-        </is>
-      </c>
-      <c r="G188" t="n">
-        <v>0</v>
-      </c>
-      <c r="H188" t="n">
-        <v>0</v>
-      </c>
-      <c r="I188" t="n">
-        <v>0</v>
-      </c>
-      <c r="J188" t="n">
-        <v>0</v>
-      </c>
-      <c r="K188" t="n">
-        <v>0</v>
-      </c>
-      <c r="L188" t="n">
-        <v>0</v>
-      </c>
-      <c r="M188" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N188" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O188" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P188" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
-      <c r="R188" t="n">
-        <v>0</v>
-      </c>
-      <c r="S188" t="n">
-        <v>0</v>
-      </c>
-      <c r="T188" t="n">
-        <v>0</v>
-      </c>
-      <c r="U188" t="n">
-        <v>0</v>
-      </c>
-      <c r="V188" t="n">
-        <v>0</v>
-      </c>
-      <c r="W188" t="n">
-        <v>0</v>
-      </c>
-      <c r="X188" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y188" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ188" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA188" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB188" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC188" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD188" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE188" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF188" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG188" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH188" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI188" s="3" t="n">
         <v>46115.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.17</v>
+        <v>1.36</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.61</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
-        <v>2.84</v>
+        <v>7.28</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.36</v>
+        <v>2.17</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.4</v>
+        <v>3.61</v>
       </c>
       <c r="R17" t="n">
-        <v>7.28</v>
+        <v>2.84</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.15</v>
+        <v>1.44</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="R31" t="n">
-        <v>2.35</v>
+        <v>6.35</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>7.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.65</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>2.95</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.79</v>
+        <v>2.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="R33" t="n">
-        <v>4.27</v>
+        <v>2.34</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.64</v>
+        <v>4.3</v>
       </c>
       <c r="R34" t="n">
-        <v>3.96</v>
+        <v>6.32</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="R35" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.68</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="R38" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.68</v>
+        <v>1.12</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.18</v>
+        <v>7.5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.6</v>
+        <v>19</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.15</v>
+        <v>2.68</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="R40" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>6.32</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
         <v>3.35</v>
       </c>
       <c r="R48" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R50" t="n">
-        <v>2.34</v>
+        <v>2.61</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.15</v>
+        <v>3.64</v>
       </c>
       <c r="R51" t="n">
-        <v>5.32</v>
+        <v>3.96</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.29</v>
+        <v>1.72</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.15</v>
+        <v>3.54</v>
       </c>
       <c r="R52" t="n">
-        <v>2.99</v>
+        <v>4.9</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.64</v>
+        <v>3.15</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.25</v>
+        <v>3.08</v>
       </c>
       <c r="R53" t="n">
-        <v>4.5</v>
+        <v>2.35</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.09</v>
+        <v>1.31</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.3</v>
+        <v>5.05</v>
       </c>
       <c r="R56" t="n">
-        <v>3.2</v>
+        <v>9.4</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R58" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.43</v>
+        <v>1.64</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="R61" t="n">
-        <v>2.63</v>
+        <v>4.5</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.31</v>
+        <v>7.55</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.05</v>
+        <v>4.65</v>
       </c>
       <c r="R63" t="n">
-        <v>9.4</v>
+        <v>1.33</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.72</v>
+        <v>3.2</v>
       </c>
       <c r="R65" t="n">
-        <v>9.07</v>
+        <v>3.46</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.12</v>
+        <v>1.35</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.2</v>
+        <v>4.72</v>
       </c>
       <c r="R67" t="n">
-        <v>3.46</v>
+        <v>9.07</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="R73" t="n">
-        <v>1.73</v>
+        <v>3.24</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="R75" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R80" t="n">
-        <v>4.09</v>
+        <v>3.31</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.02</v>
+        <v>4.19</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R81" t="n">
-        <v>3.31</v>
+        <v>1.77</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R86" t="n">
-        <v>2.7</v>
+        <v>3.91</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,139 +17940,139 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI89" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL89" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP89" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR89" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AS89" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AU89" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AV89" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW89" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AY89" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ89" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BA89" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BB89" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC89" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD89" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE89" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF89" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG89" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BH89" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BI89" s="3" t="n">
         <v>46115.55208333334</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,139 +18137,139 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD90" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ90" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL90" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM90" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN90" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO90" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AR90" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AS90" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AT90" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AU90" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AV90" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AW90" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX90" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AY90" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AZ90" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BA90" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BB90" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC90" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD90" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE90" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF90" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG90" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BH90" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BI90" s="3" t="n">
         <v>46115.55208333334</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>3.75</v>
+        <v>1.49</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R106" t="n">
-        <v>1.96</v>
+        <v>6.05</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="R107" t="n">
-        <v>4.25</v>
+        <v>3.65</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.65</v>
+        <v>3.56</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R108" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.39</v>
+        <v>1.59</v>
       </c>
       <c r="Q109" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="R109" t="n">
-        <v>3.16</v>
+        <v>4.95</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="Q110" t="n">
         <v>3.4</v>
       </c>
       <c r="R110" t="n">
-        <v>2.6</v>
+        <v>4.25</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.26</v>
+        <v>3.85</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R111" t="n">
-        <v>2.89</v>
+        <v>2.02</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.49</v>
+        <v>3.25</v>
       </c>
       <c r="Q112" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="R112" t="n">
-        <v>6.05</v>
+        <v>2.28</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="Q113" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="R113" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22861,17 +22861,17 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,17 +23058,17 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="R116" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>3.85</v>
+        <v>2.39</v>
       </c>
       <c r="Q117" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R117" t="n">
-        <v>2.02</v>
+        <v>3.16</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1.93</v>
+        <v>2.65</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="R118" t="n">
-        <v>3.36</v>
+        <v>2.5</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.59</v>
+        <v>1.93</v>
       </c>
       <c r="Q119" t="n">
-        <v>4.1</v>
+        <v>3.52</v>
       </c>
       <c r="R119" t="n">
-        <v>4.95</v>
+        <v>3.36</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>3.16</v>
+        <v>1.72</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="R120" t="n">
-        <v>2</v>
+        <v>4.65</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF121" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF127" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF133" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF134" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF136" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF137" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R139" t="n">
-        <v>3.7</v>
+        <v>1.85</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q140" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R140" t="n">
         <v>3.7</v>
-      </c>
-      <c r="R140" t="n">
-        <v>1.85</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.88</v>
+        <v>1.34</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.48</v>
+        <v>5.63</v>
       </c>
       <c r="R149" t="n">
-        <v>4.04</v>
+        <v>10.9</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,16 +29805,16 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF149" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG149" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH149" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI149" t="n">
         <v>0</v>
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>3.99</v>
+        <v>3</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R150" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>1.34</v>
+        <v>5.35</v>
       </c>
       <c r="Q151" t="n">
-        <v>5.63</v>
+        <v>4.05</v>
       </c>
       <c r="R151" t="n">
-        <v>10.9</v>
+        <v>1.58</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,16 +30199,16 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AF151" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="AG151" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH151" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI151" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>3</v>
+        <v>6.12</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="R152" t="n">
-        <v>2.3</v>
+        <v>1.46</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF152" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.91</v>
+        <v>1.88</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="R153" t="n">
-        <v>2.26</v>
+        <v>4.04</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>5.35</v>
+        <v>2.28</v>
       </c>
       <c r="Q154" t="n">
-        <v>4.05</v>
+        <v>3.52</v>
       </c>
       <c r="R154" t="n">
-        <v>1.58</v>
+        <v>2.58</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,10 +30790,10 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF154" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AG154" t="n">
         <v>0</v>
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>6.12</v>
+        <v>2.01</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.98</v>
+        <v>3.18</v>
       </c>
       <c r="R156" t="n">
-        <v>1.46</v>
+        <v>3.47</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,10 +31184,10 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF156" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.01</v>
+        <v>3.99</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="R157" t="n">
-        <v>3.47</v>
+        <v>1.92</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>2.28</v>
+        <v>2.91</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="R159" t="n">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31775,10 +31775,10 @@
         <v>0</v>
       </c>
       <c r="AE159" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF159" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF160" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>1.47</v>
+        <v>3.29</v>
       </c>
       <c r="Q161" t="n">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="R161" t="n">
-        <v>6.46</v>
+        <v>2.18</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF161" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33696,7 +33696,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P169" t="n">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34090,17 +34090,17 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34139,10 +34139,10 @@
         <v>0</v>
       </c>
       <c r="AE171" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF171" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q172" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34730,10 +34730,10 @@
         <v>0</v>
       </c>
       <c r="AE174" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF174" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG174" t="n">
         <v>0</v>
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -34927,10 +34927,10 @@
         <v>0</v>
       </c>
       <c r="AE175" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF175" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35075,7 +35075,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>2.39</v>
+        <v>1.66</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.26</v>
+        <v>3.65</v>
       </c>
       <c r="R177" t="n">
-        <v>2.91</v>
+        <v>5.23</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35321,10 +35321,10 @@
         <v>0</v>
       </c>
       <c r="AE177" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AF177" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG177" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35469,7 +35469,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35715,10 +35715,10 @@
         <v>0</v>
       </c>
       <c r="AE179" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF179" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG179" t="n">
         <v>0</v>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q180" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36109,10 +36109,10 @@
         <v>0</v>
       </c>
       <c r="AE181" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF181" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG181" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36306,10 +36306,10 @@
         <v>0</v>
       </c>
       <c r="AE182" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF182" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG182" t="n">
         <v>0</v>
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36700,10 +36700,10 @@
         <v>0</v>
       </c>
       <c r="AE184" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF184" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q185" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G186" t="n">

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI186"/>
+  <dimension ref="A1:BI178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="R31" t="n">
-        <v>6.35</v>
+        <v>5.32</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="R32" t="n">
-        <v>2.95</v>
+        <v>6.35</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q33" t="n">
         <v>3.25</v>
       </c>
       <c r="R33" t="n">
-        <v>2.34</v>
+        <v>2.95</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>6.32</v>
+        <v>2.34</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="R35" t="n">
-        <v>2.99</v>
+        <v>6.32</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.55</v>
+        <v>2.29</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="R37" t="n">
-        <v>5.32</v>
+        <v>2.99</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>1.12</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.35</v>
+        <v>7.5</v>
       </c>
       <c r="R38" t="n">
-        <v>3.25</v>
+        <v>19</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.64</v>
+        <v>1.85</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.22</v>
+        <v>3.64</v>
       </c>
       <c r="R50" t="n">
-        <v>2.61</v>
+        <v>3.96</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.64</v>
+        <v>3.54</v>
       </c>
       <c r="R51" t="n">
-        <v>3.96</v>
+        <v>4.9</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.72</v>
+        <v>3.15</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.54</v>
+        <v>3.08</v>
       </c>
       <c r="R52" t="n">
-        <v>4.9</v>
+        <v>2.35</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.08</v>
+        <v>3.65</v>
       </c>
       <c r="R53" t="n">
-        <v>2.35</v>
+        <v>4.27</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R62" t="n">
-        <v>4.27</v>
+        <v>3.24</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.12</v>
+        <v>1.35</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.2</v>
+        <v>4.72</v>
       </c>
       <c r="R65" t="n">
-        <v>3.46</v>
+        <v>9.07</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>9.07</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.49</v>
+        <v>2.06</v>
       </c>
       <c r="Q106" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="R106" t="n">
-        <v>6.05</v>
+        <v>3.65</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.24</v>
+        <v>3.52</v>
       </c>
       <c r="R107" t="n">
-        <v>3.65</v>
+        <v>3.36</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.78</v>
+        <v>3.75</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R110" t="n">
-        <v>4.25</v>
+        <v>1.96</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>3.85</v>
+        <v>1.49</v>
       </c>
       <c r="Q111" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="R111" t="n">
-        <v>2.02</v>
+        <v>6.05</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22467,17 +22467,17 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R113" t="n">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.26</v>
+        <v>1.78</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R114" t="n">
-        <v>2.89</v>
+        <v>4.25</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,17 +23058,17 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R116" t="n">
-        <v>2.6</v>
+        <v>3.16</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.39</v>
+        <v>2.65</v>
       </c>
       <c r="Q117" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R117" t="n">
-        <v>3.16</v>
+        <v>2.5</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.65</v>
+        <v>3.85</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R118" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="R119" t="n">
-        <v>3.36</v>
+        <v>2.28</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>1.72</v>
+        <v>3.16</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="R120" t="n">
-        <v>4.65</v>
+        <v>2</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF121" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>6.69</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="R124" t="n">
-        <v>3.87</v>
+        <v>4.65</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AF124" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF125" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>3.13</v>
+        <v>2.47</v>
       </c>
       <c r="Q126" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="R126" t="n">
-        <v>2.37</v>
+        <v>2.84</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF127" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.71</v>
+        <v>1.9</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.26</v>
+        <v>3.54</v>
       </c>
       <c r="R128" t="n">
-        <v>2.52</v>
+        <v>3.87</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AF128" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q139" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R139" t="n">
         <v>3.7</v>
-      </c>
-      <c r="R139" t="n">
-        <v>1.85</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R140" t="n">
-        <v>3.7</v>
+        <v>1.85</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.34</v>
+        <v>2.2</v>
       </c>
       <c r="Q149" t="n">
-        <v>5.63</v>
+        <v>3.35</v>
       </c>
       <c r="R149" t="n">
-        <v>10.9</v>
+        <v>2.89</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,16 +29805,16 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AF149" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AG149" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH149" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,61 +29957,61 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>3</v>
+        <v>1.34</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.6</v>
+        <v>5.63</v>
       </c>
       <c r="R150" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" t="n">
+        <v>0</v>
+      </c>
+      <c r="X150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF150" t="n">
         <v>2.3</v>
       </c>
-      <c r="S150" t="n">
-        <v>0</v>
-      </c>
-      <c r="T150" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" t="n">
-        <v>0</v>
-      </c>
-      <c r="V150" t="n">
-        <v>0</v>
-      </c>
-      <c r="W150" t="n">
-        <v>0</v>
-      </c>
-      <c r="X150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF150" t="n">
-        <v>0</v>
-      </c>
       <c r="AG150" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH150" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI150" t="n">
         <v>0</v>
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>5.35</v>
+        <v>1.39</v>
       </c>
       <c r="Q151" t="n">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="R151" t="n">
-        <v>1.58</v>
+        <v>7.28</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AF151" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>6.12</v>
+        <v>3.99</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.98</v>
+        <v>3.38</v>
       </c>
       <c r="R152" t="n">
-        <v>1.46</v>
+        <v>1.92</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF152" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1.88</v>
+        <v>5.35</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.48</v>
+        <v>4.05</v>
       </c>
       <c r="R153" t="n">
-        <v>4.04</v>
+        <v>1.58</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF153" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="R154" t="n">
-        <v>2.58</v>
+        <v>4.04</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30790,10 +30790,10 @@
         <v>0</v>
       </c>
       <c r="AE154" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF154" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG154" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1.39</v>
+        <v>2.91</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="R155" t="n">
-        <v>7.28</v>
+        <v>2.26</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30987,10 +30987,10 @@
         <v>0</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF155" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG155" t="n">
         <v>0</v>
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.01</v>
+        <v>6.12</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.18</v>
+        <v>3.98</v>
       </c>
       <c r="R156" t="n">
-        <v>3.47</v>
+        <v>1.46</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,10 +31184,10 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF156" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>3.99</v>
+        <v>2.28</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="R157" t="n">
-        <v>1.92</v>
+        <v>2.58</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,10 +31381,10 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF157" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG157" t="n">
         <v>0</v>
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="R158" t="n">
-        <v>2.89</v>
+        <v>3.47</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF158" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG158" t="n">
         <v>0</v>
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R159" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q168" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33548,10 +33548,10 @@
         <v>0</v>
       </c>
       <c r="AE168" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF168" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33696,17 +33696,17 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33745,10 +33745,10 @@
         <v>0</v>
       </c>
       <c r="AE169" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF169" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33893,7 +33893,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34139,10 +34139,10 @@
         <v>0</v>
       </c>
       <c r="AE171" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF171" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34287,17 +34287,17 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P172" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34533,10 +34533,10 @@
         <v>0</v>
       </c>
       <c r="AE173" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF173" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG173" t="n">
         <v>0</v>
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -34927,10 +34927,10 @@
         <v>0</v>
       </c>
       <c r="AE175" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF175" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG175" t="n">
         <v>0</v>
@@ -35026,27 +35026,27 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35075,17 +35075,17 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P176" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q176" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35124,10 +35124,10 @@
         <v>0</v>
       </c>
       <c r="AE176" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF176" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG176" t="n">
         <v>0</v>
@@ -35214,7 +35214,7 @@
         <v>0</v>
       </c>
       <c r="BI176" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.89583333334</v>
       </c>
     </row>
     <row r="177">
@@ -35223,27 +35223,27 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35321,10 +35321,10 @@
         <v>0</v>
       </c>
       <c r="AE177" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF177" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG177" t="n">
         <v>0</v>
@@ -35411,7 +35411,7 @@
         <v>0</v>
       </c>
       <c r="BI177" s="3" t="n">
-        <v>46115.875</v>
+        <v>46115.91666666666</v>
       </c>
     </row>
     <row r="178">
@@ -35420,27 +35420,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35608,1582 +35608,6 @@
         <v>0</v>
       </c>
       <c r="BI178" s="3" t="n">
-        <v>46115.875</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>LDU Quito</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="G179" t="n">
-        <v>0</v>
-      </c>
-      <c r="H179" t="n">
-        <v>0</v>
-      </c>
-      <c r="I179" t="n">
-        <v>0</v>
-      </c>
-      <c r="J179" t="n">
-        <v>0</v>
-      </c>
-      <c r="K179" t="n">
-        <v>0</v>
-      </c>
-      <c r="L179" t="n">
-        <v>0</v>
-      </c>
-      <c r="M179" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N179" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O179" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P179" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q179" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="R179" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="S179" t="n">
-        <v>0</v>
-      </c>
-      <c r="T179" t="n">
-        <v>0</v>
-      </c>
-      <c r="U179" t="n">
-        <v>0</v>
-      </c>
-      <c r="V179" t="n">
-        <v>0</v>
-      </c>
-      <c r="W179" t="n">
-        <v>0</v>
-      </c>
-      <c r="X179" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y179" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE179" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF179" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH179" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI179" s="3" t="n">
-        <v>46115.875</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Dubočica</t>
-        </is>
-      </c>
-      <c r="G180" t="n">
-        <v>0</v>
-      </c>
-      <c r="H180" t="n">
-        <v>0</v>
-      </c>
-      <c r="I180" t="n">
-        <v>0</v>
-      </c>
-      <c r="J180" t="n">
-        <v>0</v>
-      </c>
-      <c r="K180" t="n">
-        <v>0</v>
-      </c>
-      <c r="L180" t="n">
-        <v>0</v>
-      </c>
-      <c r="M180" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N180" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O180" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P180" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
-      <c r="R180" t="n">
-        <v>0</v>
-      </c>
-      <c r="S180" t="n">
-        <v>0</v>
-      </c>
-      <c r="T180" t="n">
-        <v>0</v>
-      </c>
-      <c r="U180" t="n">
-        <v>0</v>
-      </c>
-      <c r="V180" t="n">
-        <v>0</v>
-      </c>
-      <c r="W180" t="n">
-        <v>0</v>
-      </c>
-      <c r="X180" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y180" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ180" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA180" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB180" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC180" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD180" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE180" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF180" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG180" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH180" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI180" s="3" t="n">
-        <v>46115.875</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Voždovac</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Dinamo Jug</t>
-        </is>
-      </c>
-      <c r="G181" t="n">
-        <v>0</v>
-      </c>
-      <c r="H181" t="n">
-        <v>0</v>
-      </c>
-      <c r="I181" t="n">
-        <v>0</v>
-      </c>
-      <c r="J181" t="n">
-        <v>0</v>
-      </c>
-      <c r="K181" t="n">
-        <v>0</v>
-      </c>
-      <c r="L181" t="n">
-        <v>0</v>
-      </c>
-      <c r="M181" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N181" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O181" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
-      <c r="R181" t="n">
-        <v>0</v>
-      </c>
-      <c r="S181" t="n">
-        <v>0</v>
-      </c>
-      <c r="T181" t="n">
-        <v>0</v>
-      </c>
-      <c r="U181" t="n">
-        <v>0</v>
-      </c>
-      <c r="V181" t="n">
-        <v>0</v>
-      </c>
-      <c r="W181" t="n">
-        <v>0</v>
-      </c>
-      <c r="X181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI181" s="3" t="n">
-        <v>46115.875</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Greece Super League</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Volos NFC</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>OFI</t>
-        </is>
-      </c>
-      <c r="G182" t="n">
-        <v>0</v>
-      </c>
-      <c r="H182" t="n">
-        <v>0</v>
-      </c>
-      <c r="I182" t="n">
-        <v>0</v>
-      </c>
-      <c r="J182" t="n">
-        <v>0</v>
-      </c>
-      <c r="K182" t="n">
-        <v>0</v>
-      </c>
-      <c r="L182" t="n">
-        <v>0</v>
-      </c>
-      <c r="M182" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N182" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O182" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P182" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="R182" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="S182" t="n">
-        <v>0</v>
-      </c>
-      <c r="T182" t="n">
-        <v>0</v>
-      </c>
-      <c r="U182" t="n">
-        <v>0</v>
-      </c>
-      <c r="V182" t="n">
-        <v>0</v>
-      </c>
-      <c r="W182" t="n">
-        <v>0</v>
-      </c>
-      <c r="X182" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y182" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE182" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF182" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH182" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI182" s="3" t="n">
-        <v>46115.875</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Zemun</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>FAP</t>
-        </is>
-      </c>
-      <c r="G183" t="n">
-        <v>0</v>
-      </c>
-      <c r="H183" t="n">
-        <v>0</v>
-      </c>
-      <c r="I183" t="n">
-        <v>0</v>
-      </c>
-      <c r="J183" t="n">
-        <v>0</v>
-      </c>
-      <c r="K183" t="n">
-        <v>0</v>
-      </c>
-      <c r="L183" t="n">
-        <v>0</v>
-      </c>
-      <c r="M183" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N183" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P183" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
-      <c r="R183" t="n">
-        <v>0</v>
-      </c>
-      <c r="S183" t="n">
-        <v>0</v>
-      </c>
-      <c r="T183" t="n">
-        <v>0</v>
-      </c>
-      <c r="U183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V183" t="n">
-        <v>0</v>
-      </c>
-      <c r="W183" t="n">
-        <v>0</v>
-      </c>
-      <c r="X183" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y183" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI183" s="3" t="n">
-        <v>46115.875</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Houston Dash</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="G184" t="n">
-        <v>0</v>
-      </c>
-      <c r="H184" t="n">
-        <v>0</v>
-      </c>
-      <c r="I184" t="n">
-        <v>0</v>
-      </c>
-      <c r="J184" t="n">
-        <v>0</v>
-      </c>
-      <c r="K184" t="n">
-        <v>0</v>
-      </c>
-      <c r="L184" t="n">
-        <v>0</v>
-      </c>
-      <c r="M184" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N184" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P184" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q184" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R184" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="S184" t="n">
-        <v>0</v>
-      </c>
-      <c r="T184" t="n">
-        <v>0</v>
-      </c>
-      <c r="U184" t="n">
-        <v>0</v>
-      </c>
-      <c r="V184" t="n">
-        <v>0</v>
-      </c>
-      <c r="W184" t="n">
-        <v>0</v>
-      </c>
-      <c r="X184" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y184" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE184" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF184" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY184" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH184" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI184" s="3" t="n">
-        <v>46115.89583333334</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>Chicago Red Stars</t>
-        </is>
-      </c>
-      <c r="G185" t="n">
-        <v>0</v>
-      </c>
-      <c r="H185" t="n">
-        <v>0</v>
-      </c>
-      <c r="I185" t="n">
-        <v>0</v>
-      </c>
-      <c r="J185" t="n">
-        <v>0</v>
-      </c>
-      <c r="K185" t="n">
-        <v>0</v>
-      </c>
-      <c r="L185" t="n">
-        <v>0</v>
-      </c>
-      <c r="M185" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N185" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O185" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P185" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q185" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R185" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="S185" t="n">
-        <v>0</v>
-      </c>
-      <c r="T185" t="n">
-        <v>0</v>
-      </c>
-      <c r="U185" t="n">
-        <v>0</v>
-      </c>
-      <c r="V185" t="n">
-        <v>0</v>
-      </c>
-      <c r="W185" t="n">
-        <v>0</v>
-      </c>
-      <c r="X185" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y185" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ185" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA185" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB185" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC185" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD185" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE185" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF185" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG185" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH185" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI185" s="3" t="n">
-        <v>46115.91666666666</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Gimnasia Jujuy</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>Patronato</t>
-        </is>
-      </c>
-      <c r="G186" t="n">
-        <v>0</v>
-      </c>
-      <c r="H186" t="n">
-        <v>0</v>
-      </c>
-      <c r="I186" t="n">
-        <v>0</v>
-      </c>
-      <c r="J186" t="n">
-        <v>0</v>
-      </c>
-      <c r="K186" t="n">
-        <v>0</v>
-      </c>
-      <c r="L186" t="n">
-        <v>0</v>
-      </c>
-      <c r="M186" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N186" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O186" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P186" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
-      <c r="R186" t="n">
-        <v>0</v>
-      </c>
-      <c r="S186" t="n">
-        <v>0</v>
-      </c>
-      <c r="T186" t="n">
-        <v>0</v>
-      </c>
-      <c r="U186" t="n">
-        <v>0</v>
-      </c>
-      <c r="V186" t="n">
-        <v>0</v>
-      </c>
-      <c r="W186" t="n">
-        <v>0</v>
-      </c>
-      <c r="X186" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y186" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ186" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA186" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB186" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC186" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD186" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE186" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF186" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG186" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH186" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI186" s="3" t="n">
         <v>46115.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="R13" t="n">
-        <v>4.75</v>
+        <v>7.28</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.36</v>
+        <v>8.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>5.05</v>
       </c>
       <c r="R14" t="n">
-        <v>7.28</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>8.75</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.05</v>
+        <v>3.88</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>4.75</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>3.25</v>
+        <v>2.34</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="R31" t="n">
-        <v>5.32</v>
+        <v>6.35</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>6.35</v>
+        <v>2.95</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.25</v>
+        <v>1.12</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.25</v>
+        <v>7.5</v>
       </c>
       <c r="R33" t="n">
-        <v>2.95</v>
+        <v>19</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="R34" t="n">
-        <v>2.34</v>
+        <v>6.32</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>6.32</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="Q38" t="n">
-        <v>7.5</v>
+        <v>4.15</v>
       </c>
       <c r="R38" t="n">
-        <v>19</v>
+        <v>5.32</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="R87" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R88" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>

--- a/jogos_2026-04-03.xlsx
+++ b/jogos_2026-04-03.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.36</v>
+        <v>8.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.4</v>
+        <v>5.05</v>
       </c>
       <c r="R13" t="n">
-        <v>7.28</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>8.75</v>
+        <v>2.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.05</v>
+        <v>3.61</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>2.84</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>7.28</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R30" t="n">
-        <v>2.34</v>
+        <v>2.61</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.44</v>
+        <v>2.68</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.2</v>
+        <v>3.22</v>
       </c>
       <c r="R31" t="n">
-        <v>6.35</v>
+        <v>2.57</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>1.12</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.25</v>
+        <v>7.5</v>
       </c>
       <c r="R32" t="n">
-        <v>2.95</v>
+        <v>19</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.12</v>
+        <v>1.64</v>
       </c>
       <c r="Q33" t="n">
-        <v>7.5</v>
+        <v>4.25</v>
       </c>
       <c r="R33" t="n">
-        <v>19</v>
+        <v>4.5</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.44</v>
+        <v>2.06</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="R34" t="n">
-        <v>6.32</v>
+        <v>3.25</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.29</v>
+        <v>2.68</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="R36" t="n">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="R38" t="n">
-        <v>5.32</v>
+        <v>4.27</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.06</v>
+        <v>1.47</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="R39" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.68</v>
+        <v>1.47</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.18</v>
+        <v>4.3</v>
       </c>
       <c r="R40" t="n">
-        <v>2.6</v>
+        <v>6.46</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="R41" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.22</v>
+        <v>3.54</v>
       </c>
       <c r="R44" t="n">
-        <v>2.57</v>
+        <v>4.9</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Q46" t="n">
         <v>4.3</v>
       </c>
       <c r="R46" t="n">
-        <v>6.46</v>
+        <v>6.32</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wycombe Wande